--- a/Flag/Extrair DP/planilhas/Linhas de Cuidado - Cardio Pos IAM (1).xlsx
+++ b/Flag/Extrair DP/planilhas/Linhas de Cuidado - Cardio Pos IAM (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmdpcombr-my.sharepoint.com/personal/anderson_cmdp_com_br/Documents/987 - IPIRANGA/ENFERMAGEM CMDP IPIRANGA/CMDP - LINHAS DE CUIDADO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="300" documentId="8_{C2D13912-E1F9-44BA-8A54-047240FABECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EBB9877-E4EE-4728-8602-65A2F6C8D50E}"/>
+  <xr:revisionPtr revIDLastSave="306" documentId="8_{C2D13912-E1F9-44BA-8A54-047240FABECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9812CB86-BBAF-49EA-92B8-228FFF59B474}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -861,9 +861,6 @@
     <t>(11)981616620</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
     <t>THAINA DOS SANTOS NASCIMENTO</t>
   </si>
   <si>
@@ -1877,6 +1874,9 @@
   </si>
   <si>
     <t>Aguardando Contato</t>
+  </si>
+  <si>
+    <t>Pendente</t>
   </si>
   <si>
     <t>NA</t>
@@ -4556,7 +4556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9931A248-8A11-4D8E-BACD-A0C0D59E4D18}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:AU6867"/>
@@ -4749,7 +4749,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="12" customHeight="1">
+    <row r="2" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A2" s="87" t="s">
         <v>47</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="12" customHeight="1">
+    <row r="3" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A3" s="87" t="s">
         <v>65</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="12" customHeight="1">
+    <row r="4" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A4" s="87" t="s">
         <v>65</v>
       </c>
@@ -5167,7 +5167,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="12" customHeight="1">
+    <row r="5" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A5" s="87" t="s">
         <v>65</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="12" customHeight="1">
+    <row r="6" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A6" s="87" t="s">
         <v>65</v>
       </c>
@@ -5445,7 +5445,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="12" customHeight="1">
+    <row r="7" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A7" s="87" t="s">
         <v>65</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="12" customHeight="1">
+    <row r="8" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A8" s="87" t="s">
         <v>65</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="12" customHeight="1">
+    <row r="9" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A9" s="87" t="s">
         <v>65</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="12" customHeight="1">
+    <row r="10" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A10" s="87" t="s">
         <v>65</v>
       </c>
@@ -6003,7 +6003,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="12" customHeight="1">
+    <row r="11" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A11" s="87" t="s">
         <v>65</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="12" customHeight="1">
+    <row r="12" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A12" s="87" t="s">
         <v>65</v>
       </c>
@@ -6281,7 +6281,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="12" customHeight="1">
+    <row r="13" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A13" s="87" t="s">
         <v>65</v>
       </c>
@@ -6413,7 +6413,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="12" customHeight="1">
+    <row r="14" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A14" s="87" t="s">
         <v>65</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="12" customHeight="1">
+    <row r="15" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A15" s="87" t="s">
         <v>65</v>
       </c>
@@ -6679,7 +6679,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="12" customHeight="1">
+    <row r="16" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A16" s="87" t="s">
         <v>65</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="12" customHeight="1">
+    <row r="17" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A17" s="87" t="s">
         <v>65</v>
       </c>
@@ -6947,7 +6947,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="18" spans="1:47" ht="12" customHeight="1">
+    <row r="18" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A18" s="87" t="s">
         <v>65</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="19" spans="1:47" ht="12" customHeight="1">
+    <row r="19" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A19" s="87" t="s">
         <v>65</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="20" spans="1:47" ht="12" customHeight="1">
+    <row r="20" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A20" s="87" t="s">
         <v>65</v>
       </c>
@@ -7347,7 +7347,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="21" spans="1:47" ht="12" customHeight="1">
+    <row r="21" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A21" s="87" t="s">
         <v>65</v>
       </c>
@@ -7481,7 +7481,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="22" spans="1:47" ht="12" customHeight="1">
+    <row r="22" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A22" s="87" t="s">
         <v>65</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="23" spans="1:47" ht="12" customHeight="1">
+    <row r="23" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A23" s="87" t="s">
         <v>65</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="24" spans="1:47" ht="12" customHeight="1">
+    <row r="24" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A24" s="87" t="s">
         <v>65</v>
       </c>
@@ -7855,7 +7855,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="25" spans="1:47" ht="12" customHeight="1">
+    <row r="25" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A25" s="87" t="s">
         <v>65</v>
       </c>
@@ -7975,7 +7975,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="26" spans="1:47" ht="12" customHeight="1">
+    <row r="26" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A26" s="87" t="s">
         <v>65</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="27" spans="1:47" ht="12" customHeight="1">
+    <row r="27" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A27" s="87" t="s">
         <v>65</v>
       </c>
@@ -8227,7 +8227,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="28" spans="1:47" ht="12" customHeight="1">
+    <row r="28" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A28" s="87" t="s">
         <v>65</v>
       </c>
@@ -8359,7 +8359,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="29" spans="1:47" ht="12" customHeight="1">
+    <row r="29" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A29" s="87" t="s">
         <v>65</v>
       </c>
@@ -8491,7 +8491,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="30" spans="1:47" ht="12" customHeight="1">
+    <row r="30" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A30" s="87" t="s">
         <v>65</v>
       </c>
@@ -8623,7 +8623,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="31" spans="1:47" ht="12" customHeight="1">
+    <row r="31" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A31" s="87" t="s">
         <v>65</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="32" spans="1:47" ht="12" customHeight="1">
+    <row r="32" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A32" s="87" t="s">
         <v>65</v>
       </c>
@@ -8875,7 +8875,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="33" spans="1:47" ht="12" customHeight="1">
+    <row r="33" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A33" s="87" t="s">
         <v>65</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="34" spans="1:47" ht="12" customHeight="1">
+    <row r="34" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A34" s="87" t="s">
         <v>65</v>
       </c>
@@ -9127,7 +9127,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="35" spans="1:47" ht="12" customHeight="1">
+    <row r="35" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A35" s="87" t="s">
         <v>65</v>
       </c>
@@ -9259,7 +9259,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="36" spans="1:47" ht="12" customHeight="1">
+    <row r="36" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A36" s="87" t="s">
         <v>65</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="37" spans="1:47" ht="12" customHeight="1">
+    <row r="37" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A37" s="87" t="s">
         <v>65</v>
       </c>
@@ -9523,7 +9523,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="38" spans="1:47" ht="12" customHeight="1">
+    <row r="38" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A38" s="87" t="s">
         <v>65</v>
       </c>
@@ -9655,7 +9655,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="39" spans="1:47" ht="12" customHeight="1">
+    <row r="39" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A39" s="87" t="s">
         <v>65</v>
       </c>
@@ -9787,7 +9787,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="40" spans="1:47" ht="12" customHeight="1">
+    <row r="40" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A40" s="87" t="s">
         <v>65</v>
       </c>
@@ -9919,7 +9919,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="41" spans="1:47" ht="12" customHeight="1">
+    <row r="41" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A41" s="87" t="s">
         <v>65</v>
       </c>
@@ -10051,7 +10051,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="42" spans="1:47" ht="12" customHeight="1">
+    <row r="42" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A42" s="87" t="s">
         <v>65</v>
       </c>
@@ -10183,7 +10183,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="43" spans="1:47" ht="12" customHeight="1">
+    <row r="43" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A43" s="87" t="s">
         <v>65</v>
       </c>
@@ -10315,7 +10315,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="44" spans="1:47" ht="12" customHeight="1">
+    <row r="44" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A44" s="87" t="s">
         <v>65</v>
       </c>
@@ -10435,7 +10435,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="45" spans="1:47" ht="12" customHeight="1">
+    <row r="45" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A45" s="87" t="s">
         <v>65</v>
       </c>
@@ -10567,7 +10567,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="46" spans="1:47" ht="12" customHeight="1">
+    <row r="46" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A46" s="87" t="s">
         <v>65</v>
       </c>
@@ -10699,7 +10699,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="47" spans="1:47" ht="12" customHeight="1">
+    <row r="47" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A47" s="87" t="s">
         <v>65</v>
       </c>
@@ -10831,7 +10831,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="48" spans="1:47" ht="12" customHeight="1">
+    <row r="48" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A48" s="87" t="s">
         <v>65</v>
       </c>
@@ -10961,7 +10961,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="49" spans="1:47" ht="12" customHeight="1">
+    <row r="49" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A49" s="87" t="s">
         <v>65</v>
       </c>
@@ -11093,7 +11093,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="50" spans="1:47" ht="12" customHeight="1">
+    <row r="50" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A50" s="87" t="s">
         <v>65</v>
       </c>
@@ -11225,7 +11225,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="51" spans="1:47" ht="12" customHeight="1">
+    <row r="51" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A51" s="87" t="s">
         <v>65</v>
       </c>
@@ -11345,7 +11345,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="52" spans="1:47" ht="12" customHeight="1">
+    <row r="52" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A52" s="87" t="s">
         <v>65</v>
       </c>
@@ -11477,7 +11477,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="53" spans="1:47" ht="12" customHeight="1">
+    <row r="53" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A53" s="87" t="s">
         <v>65</v>
       </c>
@@ -11609,7 +11609,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="54" spans="1:47" ht="12" customHeight="1">
+    <row r="54" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A54" s="87" t="s">
         <v>65</v>
       </c>
@@ -11729,7 +11729,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="55" spans="1:47" ht="12" customHeight="1">
+    <row r="55" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A55" s="87" t="s">
         <v>65</v>
       </c>
@@ -11861,7 +11861,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="56" spans="1:47" ht="12" customHeight="1">
+    <row r="56" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A56" s="87" t="s">
         <v>65</v>
       </c>
@@ -11981,7 +11981,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="57" spans="1:47" ht="12" customHeight="1">
+    <row r="57" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A57" s="87" t="s">
         <v>65</v>
       </c>
@@ -12113,7 +12113,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="58" spans="1:47" ht="12" customHeight="1">
+    <row r="58" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A58" s="87" t="s">
         <v>65</v>
       </c>
@@ -12233,7 +12233,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="59" spans="1:47" ht="12" customHeight="1">
+    <row r="59" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A59" s="87" t="s">
         <v>65</v>
       </c>
@@ -12353,7 +12353,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="60" spans="1:47" ht="12" customHeight="1">
+    <row r="60" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A60" s="87" t="s">
         <v>47</v>
       </c>
@@ -12493,7 +12493,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="61" spans="1:47" ht="12" customHeight="1">
+    <row r="61" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A61" s="87" t="s">
         <v>47</v>
       </c>
@@ -12633,7 +12633,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="62" spans="1:47" ht="12" customHeight="1">
+    <row r="62" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A62" s="87" t="s">
         <v>47</v>
       </c>
@@ -12773,7 +12773,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="63" spans="1:47" ht="12" customHeight="1">
+    <row r="63" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A63" s="87" t="s">
         <v>47</v>
       </c>
@@ -12913,7 +12913,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="64" spans="1:47" ht="12" customHeight="1">
+    <row r="64" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A64" s="87" t="s">
         <v>47</v>
       </c>
@@ -13051,7 +13051,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="65" spans="1:47" ht="12" customHeight="1">
+    <row r="65" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A65" s="87" t="s">
         <v>47</v>
       </c>
@@ -13183,7 +13183,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="66" spans="1:47" ht="12" customHeight="1">
+    <row r="66" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A66" s="87" t="s">
         <v>47</v>
       </c>
@@ -13317,7 +13317,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="67" spans="1:47" ht="12" customHeight="1">
+    <row r="67" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A67" s="87" t="s">
         <v>47</v>
       </c>
@@ -13451,7 +13451,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="68" spans="1:47" ht="12" customHeight="1">
+    <row r="68" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A68" s="87" t="s">
         <v>47</v>
       </c>
@@ -13585,7 +13585,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="69" spans="1:47" ht="12" customHeight="1">
+    <row r="69" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A69" s="87" t="s">
         <v>47</v>
       </c>
@@ -13725,7 +13725,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="70" spans="1:47" ht="12" customHeight="1">
+    <row r="70" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A70" s="87" t="s">
         <v>47</v>
       </c>
@@ -13859,7 +13859,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="71" spans="1:47" ht="12" customHeight="1">
+    <row r="71" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A71" s="87" t="s">
         <v>47</v>
       </c>
@@ -13985,7 +13985,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="72" spans="1:47" ht="12" customHeight="1">
+    <row r="72" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A72" s="87" t="s">
         <v>47</v>
       </c>
@@ -14111,7 +14111,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="73" spans="1:47" ht="12" customHeight="1">
+    <row r="73" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A73" s="87" t="s">
         <v>47</v>
       </c>
@@ -14245,7 +14245,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="74" spans="1:47" ht="12" customHeight="1">
+    <row r="74" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A74" s="87" t="s">
         <v>47</v>
       </c>
@@ -14371,7 +14371,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="75" spans="1:47" ht="12" customHeight="1">
+    <row r="75" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A75" s="87" t="s">
         <v>47</v>
       </c>
@@ -14503,7 +14503,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="76" spans="1:47" ht="12" customHeight="1">
+    <row r="76" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A76" s="87" t="s">
         <v>47</v>
       </c>
@@ -14629,7 +14629,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="77" spans="1:47" ht="12" customHeight="1">
+    <row r="77" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A77" s="87" t="s">
         <v>47</v>
       </c>
@@ -14755,7 +14755,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="78" spans="1:47" ht="12" customHeight="1">
+    <row r="78" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A78" s="87" t="s">
         <v>47</v>
       </c>
@@ -14881,7 +14881,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="79" spans="1:47" ht="12" customHeight="1">
+    <row r="79" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A79" s="87" t="s">
         <v>47</v>
       </c>
@@ -15013,7 +15013,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="80" spans="1:47" ht="12" customHeight="1">
+    <row r="80" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A80" s="87" t="s">
         <v>47</v>
       </c>
@@ -15145,7 +15145,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="81" spans="1:47" ht="12" customHeight="1">
+    <row r="81" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A81" s="87" t="s">
         <v>47</v>
       </c>
@@ -15356,7 +15356,7 @@
         <v>62</v>
       </c>
       <c r="AJ82" s="100" t="s">
-        <v>264</v>
+        <v>47</v>
       </c>
       <c r="AK82" s="100" t="s">
         <v>47</v>
@@ -15401,7 +15401,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="83" spans="1:47" ht="12" customHeight="1">
+    <row r="83" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A83" s="87" t="s">
         <v>47</v>
       </c>
@@ -15418,7 +15418,7 @@
         <v>84926662</v>
       </c>
       <c r="F83" s="220" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G83" s="92">
         <v>46290335804</v>
@@ -15441,7 +15441,7 @@
         <v>68</v>
       </c>
       <c r="O83" s="94" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P83" s="95" t="s">
         <v>55</v>
@@ -15539,7 +15539,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="84" spans="1:47" ht="12" customHeight="1">
+    <row r="84" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A84" s="87" t="s">
         <v>47</v>
       </c>
@@ -15556,7 +15556,7 @@
         <v>89981677</v>
       </c>
       <c r="F84" s="220" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G84" s="92">
         <v>9394998780</v>
@@ -15579,7 +15579,7 @@
         <v>132</v>
       </c>
       <c r="O84" s="94" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P84" s="95" t="s">
         <v>55</v>
@@ -15665,7 +15665,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="85" spans="1:47" ht="12" customHeight="1">
+    <row r="85" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A85" s="87" t="s">
         <v>47</v>
       </c>
@@ -15682,7 +15682,7 @@
         <v>483828165</v>
       </c>
       <c r="F85" s="220" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G85" s="92">
         <v>26989310782</v>
@@ -15705,7 +15705,7 @@
         <v>107</v>
       </c>
       <c r="O85" s="94" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P85" s="95" t="s">
         <v>55</v>
@@ -15791,7 +15791,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="86" spans="1:47" ht="12" customHeight="1">
+    <row r="86" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A86" s="87" t="s">
         <v>65</v>
       </c>
@@ -15808,7 +15808,7 @@
         <v>93322178</v>
       </c>
       <c r="F86" s="220" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G86" s="92"/>
       <c r="H86" s="93">
@@ -15821,17 +15821,17 @@
         <v>51</v>
       </c>
       <c r="K86" s="89" t="s">
+        <v>271</v>
+      </c>
+      <c r="L86" s="89" t="s">
         <v>272</v>
-      </c>
-      <c r="L86" s="89" t="s">
-        <v>273</v>
       </c>
       <c r="M86" s="89"/>
       <c r="N86" s="89" t="s">
         <v>129</v>
       </c>
       <c r="O86" s="94" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P86" s="95" t="s">
         <v>55</v>
@@ -15923,7 +15923,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="87" spans="1:47" ht="12" customHeight="1">
+    <row r="87" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A87" s="87" t="s">
         <v>65</v>
       </c>
@@ -15940,7 +15940,7 @@
         <v>123911656</v>
       </c>
       <c r="F87" s="220" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G87" s="92"/>
       <c r="H87" s="93">
@@ -15956,14 +15956,14 @@
         <v>52</v>
       </c>
       <c r="L87" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M87" s="89"/>
       <c r="N87" s="89" t="s">
         <v>95</v>
       </c>
       <c r="O87" s="94" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P87" s="95" t="s">
         <v>55</v>
@@ -16043,7 +16043,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="88" spans="1:47" ht="12" customHeight="1">
+    <row r="88" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A88" s="87" t="s">
         <v>65</v>
       </c>
@@ -16060,7 +16060,7 @@
         <v>28226658</v>
       </c>
       <c r="F88" s="220" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G88" s="92"/>
       <c r="H88" s="93">
@@ -16076,14 +16076,14 @@
         <v>52</v>
       </c>
       <c r="L88" s="89" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M88" s="89"/>
       <c r="N88" s="89" t="s">
         <v>95</v>
       </c>
       <c r="O88" s="94" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P88" s="95" t="s">
         <v>55</v>
@@ -16175,7 +16175,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="89" spans="1:47" ht="12" customHeight="1">
+    <row r="89" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A89" s="87" t="s">
         <v>65</v>
       </c>
@@ -16192,7 +16192,7 @@
         <v>75800772</v>
       </c>
       <c r="F89" s="220" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G89" s="92"/>
       <c r="H89" s="93">
@@ -16208,14 +16208,14 @@
         <v>52</v>
       </c>
       <c r="L89" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M89" s="89"/>
       <c r="N89" s="89" t="s">
         <v>79</v>
       </c>
       <c r="O89" s="94" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P89" s="95" t="s">
         <v>55</v>
@@ -16307,7 +16307,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="90" spans="1:47" ht="12" customHeight="1">
+    <row r="90" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A90" s="87" t="s">
         <v>65</v>
       </c>
@@ -16324,7 +16324,7 @@
         <v>128560118</v>
       </c>
       <c r="F90" s="220" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G90" s="92"/>
       <c r="H90" s="93">
@@ -16340,14 +16340,14 @@
         <v>52</v>
       </c>
       <c r="L90" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M90" s="89"/>
       <c r="N90" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O90" s="94" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P90" s="95" t="s">
         <v>55</v>
@@ -16439,7 +16439,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="91" spans="1:47" ht="12" customHeight="1">
+    <row r="91" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A91" s="87" t="s">
         <v>65</v>
       </c>
@@ -16456,7 +16456,7 @@
         <v>300974698</v>
       </c>
       <c r="F91" s="220" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G91" s="92"/>
       <c r="H91" s="93">
@@ -16472,14 +16472,14 @@
         <v>52</v>
       </c>
       <c r="L91" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M91" s="89"/>
       <c r="N91" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O91" s="94" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P91" s="95" t="s">
         <v>55</v>
@@ -16559,7 +16559,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="92" spans="1:47" ht="12" customHeight="1">
+    <row r="92" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A92" s="87" t="s">
         <v>65</v>
       </c>
@@ -16576,7 +16576,7 @@
         <v>124994059</v>
       </c>
       <c r="F92" s="220" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G92" s="92"/>
       <c r="H92" s="93">
@@ -16592,14 +16592,14 @@
         <v>52</v>
       </c>
       <c r="L92" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M92" s="89"/>
       <c r="N92" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O92" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P92" s="95" t="s">
         <v>55</v>
@@ -16691,7 +16691,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="93" spans="1:47" ht="12" customHeight="1">
+    <row r="93" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A93" s="87" t="s">
         <v>65</v>
       </c>
@@ -16708,7 +16708,7 @@
         <v>128180234</v>
       </c>
       <c r="F93" s="220" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G93" s="92"/>
       <c r="H93" s="93">
@@ -16724,14 +16724,14 @@
         <v>52</v>
       </c>
       <c r="L93" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M93" s="89"/>
       <c r="N93" s="89" t="s">
         <v>95</v>
       </c>
       <c r="O93" s="94" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P93" s="95" t="s">
         <v>55</v>
@@ -16823,7 +16823,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="94" spans="1:47" ht="12" customHeight="1">
+    <row r="94" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A94" s="87" t="s">
         <v>65</v>
       </c>
@@ -16840,7 +16840,7 @@
         <v>301019142</v>
       </c>
       <c r="F94" s="220" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G94" s="92"/>
       <c r="H94" s="93">
@@ -16856,14 +16856,14 @@
         <v>52</v>
       </c>
       <c r="L94" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M94" s="89"/>
       <c r="N94" s="89" t="s">
         <v>95</v>
       </c>
       <c r="O94" s="94" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P94" s="95" t="s">
         <v>55</v>
@@ -16943,7 +16943,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="95" spans="1:47" ht="12" customHeight="1">
+    <row r="95" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A95" s="87" t="s">
         <v>65</v>
       </c>
@@ -16960,7 +16960,7 @@
         <v>316484679</v>
       </c>
       <c r="F95" s="220" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G95" s="92"/>
       <c r="H95" s="93">
@@ -16973,17 +16973,17 @@
         <v>51</v>
       </c>
       <c r="K95" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L95" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M95" s="89"/>
       <c r="N95" s="89" t="s">
         <v>107</v>
       </c>
       <c r="O95" s="94" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P95" s="95" t="s">
         <v>55</v>
@@ -17075,7 +17075,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="96" spans="1:47" ht="12" customHeight="1">
+    <row r="96" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A96" s="87" t="s">
         <v>65</v>
       </c>
@@ -17092,7 +17092,7 @@
         <v>437341062</v>
       </c>
       <c r="F96" s="220" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G96" s="92"/>
       <c r="H96" s="93">
@@ -17105,17 +17105,17 @@
         <v>51</v>
       </c>
       <c r="K96" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L96" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M96" s="89"/>
       <c r="N96" s="89" t="s">
         <v>258</v>
       </c>
       <c r="O96" s="94" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P96" s="95" t="s">
         <v>55</v>
@@ -17205,7 +17205,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="97" spans="1:47" ht="12" customHeight="1">
+    <row r="97" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A97" s="87" t="s">
         <v>65</v>
       </c>
@@ -17222,7 +17222,7 @@
         <v>449808491</v>
       </c>
       <c r="F97" s="220" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G97" s="92"/>
       <c r="H97" s="93">
@@ -17238,14 +17238,14 @@
         <v>52</v>
       </c>
       <c r="L97" s="89" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M97" s="89"/>
       <c r="N97" s="89" t="s">
         <v>107</v>
       </c>
       <c r="O97" s="94" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P97" s="95" t="s">
         <v>55</v>
@@ -17325,7 +17325,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="98" spans="1:47" ht="12" customHeight="1">
+    <row r="98" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A98" s="87" t="s">
         <v>65</v>
       </c>
@@ -17342,7 +17342,7 @@
         <v>450218201</v>
       </c>
       <c r="F98" s="220" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G98" s="92"/>
       <c r="H98" s="93">
@@ -17358,14 +17358,14 @@
         <v>52</v>
       </c>
       <c r="L98" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M98" s="89"/>
       <c r="N98" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O98" s="94" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P98" s="95" t="s">
         <v>55</v>
@@ -17445,7 +17445,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="99" spans="1:47" ht="12" customHeight="1">
+    <row r="99" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A99" s="87" t="s">
         <v>65</v>
       </c>
@@ -17462,7 +17462,7 @@
         <v>450249298</v>
       </c>
       <c r="F99" s="220" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G99" s="92"/>
       <c r="H99" s="93">
@@ -17478,14 +17478,14 @@
         <v>52</v>
       </c>
       <c r="L99" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M99" s="89"/>
       <c r="N99" s="89" t="s">
         <v>53</v>
       </c>
       <c r="O99" s="94" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P99" s="95" t="s">
         <v>55</v>
@@ -17565,7 +17565,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="100" spans="1:47" ht="12" customHeight="1">
+    <row r="100" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A100" s="87" t="s">
         <v>65</v>
       </c>
@@ -17582,7 +17582,7 @@
         <v>450509133</v>
       </c>
       <c r="F100" s="220" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G100" s="92"/>
       <c r="H100" s="93">
@@ -17598,14 +17598,14 @@
         <v>52</v>
       </c>
       <c r="L100" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M100" s="89"/>
       <c r="N100" s="89" t="s">
         <v>53</v>
       </c>
       <c r="O100" s="94" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P100" s="95" t="s">
         <v>55</v>
@@ -17685,7 +17685,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="101" spans="1:47" ht="12" customHeight="1">
+    <row r="101" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A101" s="87" t="s">
         <v>65</v>
       </c>
@@ -17702,7 +17702,7 @@
         <v>451016505</v>
       </c>
       <c r="F101" s="220" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G101" s="92"/>
       <c r="H101" s="93">
@@ -17718,14 +17718,14 @@
         <v>52</v>
       </c>
       <c r="L101" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M101" s="89"/>
       <c r="N101" s="89" t="s">
         <v>92</v>
       </c>
       <c r="O101" s="94" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P101" s="95" t="s">
         <v>55</v>
@@ -17805,7 +17805,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="102" spans="1:47" ht="12" customHeight="1">
+    <row r="102" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A102" s="87" t="s">
         <v>65</v>
       </c>
@@ -17822,7 +17822,7 @@
         <v>451170407</v>
       </c>
       <c r="F102" s="220" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G102" s="92"/>
       <c r="H102" s="93">
@@ -17838,14 +17838,14 @@
         <v>52</v>
       </c>
       <c r="L102" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M102" s="89"/>
       <c r="N102" s="89" t="s">
         <v>92</v>
       </c>
       <c r="O102" s="94" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P102" s="95" t="s">
         <v>55</v>
@@ -17925,7 +17925,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="103" spans="1:47" ht="12" customHeight="1">
+    <row r="103" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A103" s="87" t="s">
         <v>65</v>
       </c>
@@ -17942,7 +17942,7 @@
         <v>451560612</v>
       </c>
       <c r="F103" s="220" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G103" s="92"/>
       <c r="H103" s="93">
@@ -17958,14 +17958,14 @@
         <v>52</v>
       </c>
       <c r="L103" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M103" s="89"/>
       <c r="N103" s="89" t="s">
         <v>95</v>
       </c>
       <c r="O103" s="94" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P103" s="95" t="s">
         <v>55</v>
@@ -18045,7 +18045,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="104" spans="1:47" ht="12" customHeight="1">
+    <row r="104" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A104" s="87" t="s">
         <v>65</v>
       </c>
@@ -18062,7 +18062,7 @@
         <v>451580907</v>
       </c>
       <c r="F104" s="220" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G104" s="92"/>
       <c r="H104" s="93">
@@ -18078,14 +18078,14 @@
         <v>52</v>
       </c>
       <c r="L104" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M104" s="89"/>
       <c r="N104" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O104" s="94" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P104" s="95" t="s">
         <v>55</v>
@@ -18165,7 +18165,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="105" spans="1:47" ht="12" customHeight="1">
+    <row r="105" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A105" s="87" t="s">
         <v>65</v>
       </c>
@@ -18182,7 +18182,7 @@
         <v>451591151</v>
       </c>
       <c r="F105" s="220" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G105" s="92"/>
       <c r="H105" s="93">
@@ -18198,14 +18198,14 @@
         <v>52</v>
       </c>
       <c r="L105" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M105" s="89"/>
       <c r="N105" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O105" s="94" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P105" s="95" t="s">
         <v>55</v>
@@ -18285,7 +18285,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="106" spans="1:47" ht="12" customHeight="1">
+    <row r="106" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A106" s="87" t="s">
         <v>65</v>
       </c>
@@ -18302,7 +18302,7 @@
         <v>451779177</v>
       </c>
       <c r="F106" s="220" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G106" s="92"/>
       <c r="H106" s="93">
@@ -18318,14 +18318,14 @@
         <v>52</v>
       </c>
       <c r="L106" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M106" s="89"/>
       <c r="N106" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O106" s="94" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P106" s="95" t="s">
         <v>55</v>
@@ -18405,7 +18405,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="107" spans="1:47" ht="12" customHeight="1">
+    <row r="107" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A107" s="87" t="s">
         <v>65</v>
       </c>
@@ -18422,7 +18422,7 @@
         <v>451835298</v>
       </c>
       <c r="F107" s="220" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G107" s="92"/>
       <c r="H107" s="93">
@@ -18438,14 +18438,14 @@
         <v>52</v>
       </c>
       <c r="L107" s="89" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M107" s="89"/>
       <c r="N107" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O107" s="94" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P107" s="95" t="s">
         <v>55</v>
@@ -18525,7 +18525,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="108" spans="1:47" ht="12" customHeight="1">
+    <row r="108" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A108" s="87" t="s">
         <v>65</v>
       </c>
@@ -18542,7 +18542,7 @@
         <v>451592743</v>
       </c>
       <c r="F108" s="220" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G108" s="92"/>
       <c r="H108" s="93">
@@ -18558,14 +18558,14 @@
         <v>52</v>
       </c>
       <c r="L108" s="89" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M108" s="89"/>
       <c r="N108" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O108" s="94" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P108" s="95" t="s">
         <v>55</v>
@@ -18657,7 +18657,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="109" spans="1:47" ht="12" customHeight="1">
+    <row r="109" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A109" s="87" t="s">
         <v>65</v>
       </c>
@@ -18674,7 +18674,7 @@
         <v>451747500</v>
       </c>
       <c r="F109" s="220" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G109" s="92"/>
       <c r="H109" s="93">
@@ -18690,14 +18690,14 @@
         <v>52</v>
       </c>
       <c r="L109" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M109" s="89"/>
       <c r="N109" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O109" s="94" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P109" s="95" t="s">
         <v>55</v>
@@ -18789,7 +18789,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="110" spans="1:47" ht="12" customHeight="1">
+    <row r="110" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A110" s="87" t="s">
         <v>65</v>
       </c>
@@ -18806,7 +18806,7 @@
         <v>452208777</v>
       </c>
       <c r="F110" s="220" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G110" s="92"/>
       <c r="H110" s="93">
@@ -18822,14 +18822,14 @@
         <v>52</v>
       </c>
       <c r="L110" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M110" s="89"/>
       <c r="N110" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O110" s="94" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P110" s="95" t="s">
         <v>55</v>
@@ -18909,7 +18909,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="111" spans="1:47" ht="12" customHeight="1">
+    <row r="111" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A111" s="87" t="s">
         <v>65</v>
       </c>
@@ -18926,7 +18926,7 @@
         <v>593964209</v>
       </c>
       <c r="F111" s="220" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G111" s="92"/>
       <c r="H111" s="93">
@@ -18942,14 +18942,14 @@
         <v>52</v>
       </c>
       <c r="L111" s="89" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M111" s="89"/>
       <c r="N111" s="89" t="s">
         <v>79</v>
       </c>
       <c r="O111" s="94" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P111" s="95" t="s">
         <v>55</v>
@@ -19029,7 +19029,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="112" spans="1:47" ht="12" customHeight="1">
+    <row r="112" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A112" s="87" t="s">
         <v>65</v>
       </c>
@@ -19046,7 +19046,7 @@
         <v>741901374</v>
       </c>
       <c r="F112" s="220" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G112" s="92"/>
       <c r="H112" s="93">
@@ -19059,17 +19059,17 @@
         <v>51</v>
       </c>
       <c r="K112" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L112" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M112" s="89"/>
       <c r="N112" s="89" t="s">
         <v>107</v>
       </c>
       <c r="O112" s="94" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P112" s="95" t="s">
         <v>55</v>
@@ -19159,7 +19159,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="113" spans="1:47" ht="12" customHeight="1">
+    <row r="113" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A113" s="87" t="s">
         <v>65</v>
       </c>
@@ -19176,7 +19176,7 @@
         <v>771015836</v>
       </c>
       <c r="F113" s="220" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G113" s="92"/>
       <c r="H113" s="93">
@@ -19192,14 +19192,14 @@
         <v>52</v>
       </c>
       <c r="L113" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M113" s="89"/>
       <c r="N113" s="89" t="s">
         <v>92</v>
       </c>
       <c r="O113" s="94" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P113" s="95" t="s">
         <v>55</v>
@@ -19279,7 +19279,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="114" spans="1:47" ht="12" customHeight="1">
+    <row r="114" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A114" s="87" t="s">
         <v>65</v>
       </c>
@@ -19296,7 +19296,7 @@
         <v>594075483</v>
       </c>
       <c r="F114" s="220" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G114" s="92">
         <v>10872920852</v>
@@ -19314,14 +19314,14 @@
         <v>52</v>
       </c>
       <c r="L114" s="89" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M114" s="89"/>
       <c r="N114" s="89" t="s">
         <v>79</v>
       </c>
       <c r="O114" s="94" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P114" s="95" t="s">
         <v>55</v>
@@ -19415,7 +19415,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="115" spans="1:47" ht="12" customHeight="1">
+    <row r="115" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A115" s="87" t="s">
         <v>65</v>
       </c>
@@ -19432,7 +19432,7 @@
         <v>790276305</v>
       </c>
       <c r="F115" s="220" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G115" s="92"/>
       <c r="H115" s="93">
@@ -19448,14 +19448,14 @@
         <v>52</v>
       </c>
       <c r="L115" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M115" s="89"/>
       <c r="N115" s="89" t="s">
         <v>53</v>
       </c>
       <c r="O115" s="94" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P115" s="95" t="s">
         <v>55</v>
@@ -19535,7 +19535,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="116" spans="1:47" ht="12" customHeight="1">
+    <row r="116" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A116" s="87" t="s">
         <v>65</v>
       </c>
@@ -19552,7 +19552,7 @@
         <v>751485209</v>
       </c>
       <c r="F116" s="220" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G116" s="92">
         <v>86569236768</v>
@@ -19567,17 +19567,17 @@
         <v>77</v>
       </c>
       <c r="K116" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L116" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M116" s="89"/>
       <c r="N116" s="89" t="s">
         <v>92</v>
       </c>
       <c r="O116" s="94" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P116" s="95" t="s">
         <v>55</v>
@@ -19671,7 +19671,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="117" spans="1:47" ht="12" customHeight="1">
+    <row r="117" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A117" s="87" t="s">
         <v>65</v>
       </c>
@@ -19688,7 +19688,7 @@
         <v>754078833</v>
       </c>
       <c r="F117" s="220" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G117" s="92"/>
       <c r="H117" s="93">
@@ -19701,17 +19701,17 @@
         <v>77</v>
       </c>
       <c r="K117" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L117" s="89" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M117" s="89"/>
       <c r="N117" s="89" t="s">
         <v>53</v>
       </c>
       <c r="O117" s="94" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P117" s="95" t="s">
         <v>55</v>
@@ -19803,7 +19803,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="118" spans="1:47" ht="12" customHeight="1">
+    <row r="118" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A118" s="87" t="s">
         <v>65</v>
       </c>
@@ -19820,7 +19820,7 @@
         <v>805177159</v>
       </c>
       <c r="F118" s="220" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G118" s="92"/>
       <c r="H118" s="93">
@@ -19836,14 +19836,14 @@
         <v>52</v>
       </c>
       <c r="L118" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M118" s="89"/>
       <c r="N118" s="89" t="s">
         <v>53</v>
       </c>
       <c r="O118" s="94" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P118" s="95" t="s">
         <v>55</v>
@@ -19923,7 +19923,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="119" spans="1:47" ht="12" customHeight="1">
+    <row r="119" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A119" s="87" t="s">
         <v>65</v>
       </c>
@@ -19940,7 +19940,7 @@
         <v>774115645</v>
       </c>
       <c r="F119" s="220" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G119" s="92"/>
       <c r="H119" s="93">
@@ -19956,14 +19956,14 @@
         <v>52</v>
       </c>
       <c r="L119" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M119" s="89"/>
       <c r="N119" s="89" t="s">
         <v>92</v>
       </c>
       <c r="O119" s="94" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P119" s="95" t="s">
         <v>55</v>
@@ -20055,7 +20055,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="120" spans="1:47" ht="12" customHeight="1">
+    <row r="120" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A120" s="87" t="s">
         <v>65</v>
       </c>
@@ -20072,7 +20072,7 @@
         <v>867294183</v>
       </c>
       <c r="F120" s="220" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G120" s="92"/>
       <c r="H120" s="93">
@@ -20088,14 +20088,14 @@
         <v>52</v>
       </c>
       <c r="L120" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M120" s="89"/>
       <c r="N120" s="89" t="s">
         <v>107</v>
       </c>
       <c r="O120" s="94" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P120" s="95" t="s">
         <v>55</v>
@@ -20187,7 +20187,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="121" spans="1:47" ht="12" customHeight="1">
+    <row r="121" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A121" s="87" t="s">
         <v>65</v>
       </c>
@@ -20204,7 +20204,7 @@
         <v>867344180</v>
       </c>
       <c r="F121" s="220" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G121" s="92"/>
       <c r="H121" s="93">
@@ -20220,14 +20220,14 @@
         <v>52</v>
       </c>
       <c r="L121" s="89" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M121" s="89"/>
       <c r="N121" s="89" t="s">
         <v>53</v>
       </c>
       <c r="O121" s="94" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P121" s="95" t="s">
         <v>55</v>
@@ -20317,7 +20317,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="122" spans="1:47" ht="12" customHeight="1">
+    <row r="122" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A122" s="87" t="s">
         <v>65</v>
       </c>
@@ -20334,7 +20334,7 @@
         <v>860405532</v>
       </c>
       <c r="F122" s="220" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G122" s="92">
         <v>8482081888</v>
@@ -20352,14 +20352,14 @@
         <v>52</v>
       </c>
       <c r="L122" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M122" s="89"/>
       <c r="N122" s="89" t="s">
         <v>53</v>
       </c>
       <c r="O122" s="94" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P122" s="95" t="s">
         <v>55</v>
@@ -20387,7 +20387,7 @@
         <v>46128</v>
       </c>
       <c r="Y122" s="98" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Z122" s="89" t="s">
         <v>60</v>
@@ -20455,7 +20455,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="123" spans="1:47" ht="12" customHeight="1">
+    <row r="123" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A123" s="87" t="s">
         <v>65</v>
       </c>
@@ -20472,7 +20472,7 @@
         <v>868333034</v>
       </c>
       <c r="F123" s="220" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G123" s="92"/>
       <c r="H123" s="93">
@@ -20488,14 +20488,14 @@
         <v>52</v>
       </c>
       <c r="L123" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M123" s="89"/>
       <c r="N123" s="89" t="s">
         <v>53</v>
       </c>
       <c r="O123" s="94" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P123" s="95" t="s">
         <v>55</v>
@@ -20575,7 +20575,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="124" spans="1:47" ht="12" customHeight="1">
+    <row r="124" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A124" s="87" t="s">
         <v>47</v>
       </c>
@@ -20592,10 +20592,10 @@
         <v>94204174</v>
       </c>
       <c r="F124" s="220" t="s">
+        <v>357</v>
+      </c>
+      <c r="G124" s="92" t="s">
         <v>358</v>
-      </c>
-      <c r="G124" s="92" t="s">
-        <v>359</v>
       </c>
       <c r="H124" s="93">
         <v>22941</v>
@@ -20643,7 +20643,7 @@
         <v>46141</v>
       </c>
       <c r="Y124" s="98" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z124" s="89" t="s">
         <v>60</v>
@@ -20709,7 +20709,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="125" spans="1:47" ht="12" customHeight="1">
+    <row r="125" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A125" s="87" t="s">
         <v>65</v>
       </c>
@@ -20726,7 +20726,7 @@
         <v>22646710</v>
       </c>
       <c r="F125" s="220" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G125" s="92">
         <v>18039400856</v>
@@ -20744,14 +20744,14 @@
         <v>52</v>
       </c>
       <c r="L125" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M125" s="89"/>
       <c r="N125" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O125" s="94" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P125" s="95" t="s">
         <v>55</v>
@@ -20781,7 +20781,7 @@
         <v>46128</v>
       </c>
       <c r="Y125" s="98" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Z125" s="89" t="s">
         <v>60</v>
@@ -20847,7 +20847,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="126" spans="1:47" ht="12" customHeight="1">
+    <row r="126" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A126" s="87" t="s">
         <v>47</v>
       </c>
@@ -20864,10 +20864,10 @@
         <v>89647515</v>
       </c>
       <c r="F126" s="220" t="s">
+        <v>363</v>
+      </c>
+      <c r="G126" s="92" t="s">
         <v>364</v>
-      </c>
-      <c r="G126" s="92" t="s">
-        <v>365</v>
       </c>
       <c r="H126" s="93">
         <v>31406</v>
@@ -20885,7 +20885,7 @@
       <c r="M126" s="89"/>
       <c r="N126" s="89"/>
       <c r="O126" s="94" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P126" s="95" t="s">
         <v>55</v>
@@ -20977,7 +20977,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="127" spans="1:47" ht="12" customHeight="1">
+    <row r="127" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A127" s="87" t="s">
         <v>47</v>
       </c>
@@ -20994,10 +20994,10 @@
         <v>200172336</v>
       </c>
       <c r="F127" s="220" t="s">
+        <v>366</v>
+      </c>
+      <c r="G127" s="92" t="s">
         <v>367</v>
-      </c>
-      <c r="G127" s="92" t="s">
-        <v>368</v>
       </c>
       <c r="H127" s="93">
         <v>19556</v>
@@ -21107,7 +21107,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="128" spans="1:47" ht="12" customHeight="1">
+    <row r="128" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A128" s="87" t="s">
         <v>47</v>
       </c>
@@ -21124,10 +21124,10 @@
         <v>800051513</v>
       </c>
       <c r="F128" s="220" t="s">
+        <v>368</v>
+      </c>
+      <c r="G128" s="92" t="s">
         <v>369</v>
-      </c>
-      <c r="G128" s="92" t="s">
-        <v>370</v>
       </c>
       <c r="H128" s="93">
         <v>16113</v>
@@ -21145,7 +21145,7 @@
       <c r="M128" s="89"/>
       <c r="N128" s="89"/>
       <c r="O128" s="94" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="P128" s="95" t="s">
         <v>55</v>
@@ -21231,7 +21231,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="129" spans="1:47" ht="12" customHeight="1">
+    <row r="129" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A129" s="87" t="s">
         <v>47</v>
       </c>
@@ -21248,10 +21248,10 @@
         <v>459388797</v>
       </c>
       <c r="F129" s="220" t="s">
+        <v>371</v>
+      </c>
+      <c r="G129" s="92" t="s">
         <v>372</v>
-      </c>
-      <c r="G129" s="92" t="s">
-        <v>373</v>
       </c>
       <c r="H129" s="93">
         <v>15732</v>
@@ -21269,7 +21269,7 @@
       <c r="M129" s="89"/>
       <c r="N129" s="89"/>
       <c r="O129" s="94" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P129" s="95" t="s">
         <v>55</v>
@@ -21355,7 +21355,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="130" spans="1:47" ht="12" customHeight="1">
+    <row r="130" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A130" s="87" t="s">
         <v>47</v>
       </c>
@@ -21372,10 +21372,10 @@
         <v>88520233</v>
       </c>
       <c r="F130" s="220" t="s">
+        <v>374</v>
+      </c>
+      <c r="G130" s="92" t="s">
         <v>375</v>
-      </c>
-      <c r="G130" s="92" t="s">
-        <v>376</v>
       </c>
       <c r="H130" s="93">
         <v>30364</v>
@@ -21393,7 +21393,7 @@
       <c r="M130" s="89"/>
       <c r="N130" s="89"/>
       <c r="O130" s="94" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P130" s="95" t="s">
         <v>55</v>
@@ -21432,13 +21432,13 @@
       </c>
       <c r="AC130" s="120"/>
       <c r="AD130" s="89" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AE130" s="89">
         <v>36</v>
       </c>
       <c r="AF130" s="99" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG130" s="99"/>
       <c r="AH130" s="99" t="s">
@@ -21493,7 +21493,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="131" spans="1:47" ht="12" customHeight="1">
+    <row r="131" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A131" s="87" t="s">
         <v>47</v>
       </c>
@@ -21510,10 +21510,10 @@
         <v>81466007</v>
       </c>
       <c r="F131" s="220" t="s">
+        <v>379</v>
+      </c>
+      <c r="G131" s="92" t="s">
         <v>380</v>
-      </c>
-      <c r="G131" s="92" t="s">
-        <v>381</v>
       </c>
       <c r="H131" s="93">
         <v>24167</v>
@@ -21531,7 +21531,7 @@
       <c r="M131" s="89"/>
       <c r="N131" s="89"/>
       <c r="O131" s="94" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P131" s="95" t="s">
         <v>55</v>
@@ -21576,7 +21576,7 @@
         <v>52</v>
       </c>
       <c r="AF131" s="99" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG131" s="99"/>
       <c r="AH131" s="99" t="s">
@@ -21631,7 +21631,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="132" spans="1:47" ht="12" customHeight="1">
+    <row r="132" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A132" s="87" t="s">
         <v>47</v>
       </c>
@@ -21648,10 +21648,10 @@
         <v>95305125</v>
       </c>
       <c r="F132" s="220" t="s">
+        <v>383</v>
+      </c>
+      <c r="G132" s="92" t="s">
         <v>384</v>
-      </c>
-      <c r="G132" s="92" t="s">
-        <v>385</v>
       </c>
       <c r="H132" s="93">
         <v>31537</v>
@@ -21669,7 +21669,7 @@
       <c r="M132" s="89"/>
       <c r="N132" s="89"/>
       <c r="O132" s="94" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P132" s="95" t="s">
         <v>55</v>
@@ -21755,7 +21755,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="133" spans="1:47" ht="12" customHeight="1">
+    <row r="133" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A133" s="87" t="s">
         <v>65</v>
       </c>
@@ -21772,7 +21772,7 @@
         <v>82825103</v>
       </c>
       <c r="F133" s="220" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G133" s="92"/>
       <c r="H133" s="93">
@@ -21785,17 +21785,17 @@
         <v>51</v>
       </c>
       <c r="K133" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L133" s="89" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M133" s="89"/>
       <c r="N133" s="89" t="s">
         <v>92</v>
       </c>
       <c r="O133" s="94" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P133" s="95" t="s">
         <v>55</v>
@@ -21840,7 +21840,7 @@
         <v>68</v>
       </c>
       <c r="AF133" s="99" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG133" s="99"/>
       <c r="AH133" s="99"/>
@@ -21893,7 +21893,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="134" spans="1:47" ht="12" customHeight="1">
+    <row r="134" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A134" s="87" t="s">
         <v>65</v>
       </c>
@@ -21910,7 +21910,7 @@
         <v>301142025</v>
       </c>
       <c r="F134" s="220" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G134" s="92"/>
       <c r="H134" s="93">
@@ -21926,14 +21926,14 @@
         <v>52</v>
       </c>
       <c r="L134" s="89" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M134" s="89"/>
       <c r="N134" s="89" t="s">
         <v>95</v>
       </c>
       <c r="O134" s="94" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="P134" s="95" t="s">
         <v>55</v>
@@ -21972,7 +21972,7 @@
       </c>
       <c r="AC134" s="120"/>
       <c r="AD134" s="89" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AE134" s="89">
         <v>36</v>
@@ -22033,7 +22033,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="135" spans="1:47" ht="12" customHeight="1">
+    <row r="135" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A135" s="87" t="s">
         <v>65</v>
       </c>
@@ -22050,7 +22050,7 @@
         <v>451816820</v>
       </c>
       <c r="F135" s="220" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G135" s="92"/>
       <c r="H135" s="93">
@@ -22066,14 +22066,14 @@
         <v>52</v>
       </c>
       <c r="L135" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M135" s="89"/>
       <c r="N135" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O135" s="94" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P135" s="95" t="s">
         <v>55</v>
@@ -22118,7 +22118,7 @@
         <v>48</v>
       </c>
       <c r="AF135" s="99" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG135" s="99"/>
       <c r="AH135" s="99" t="s">
@@ -22173,7 +22173,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="136" spans="1:47" ht="12" customHeight="1">
+    <row r="136" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A136" s="87" t="s">
         <v>65</v>
       </c>
@@ -22190,7 +22190,7 @@
         <v>451847512</v>
       </c>
       <c r="F136" s="220" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G136" s="92"/>
       <c r="H136" s="93">
@@ -22206,14 +22206,14 @@
         <v>52</v>
       </c>
       <c r="L136" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M136" s="89"/>
       <c r="N136" s="89" t="s">
         <v>151</v>
       </c>
       <c r="O136" s="94" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P136" s="95" t="s">
         <v>55</v>
@@ -22313,7 +22313,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="137" spans="1:47" ht="12" customHeight="1">
+    <row r="137" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A137" s="87" t="s">
         <v>65</v>
       </c>
@@ -22330,7 +22330,7 @@
         <v>594117267</v>
       </c>
       <c r="F137" s="220" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G137" s="92"/>
       <c r="H137" s="93">
@@ -22346,14 +22346,14 @@
         <v>52</v>
       </c>
       <c r="L137" s="89" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M137" s="89"/>
       <c r="N137" s="89" t="s">
         <v>79</v>
       </c>
       <c r="O137" s="94" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="P137" s="95" t="s">
         <v>55</v>
@@ -22453,7 +22453,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="138" spans="1:47" ht="12" customHeight="1">
+    <row r="138" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A138" s="87" t="s">
         <v>65</v>
       </c>
@@ -22470,7 +22470,7 @@
         <v>799416312</v>
       </c>
       <c r="F138" s="220" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G138" s="92">
         <v>27652850800</v>
@@ -22488,14 +22488,14 @@
         <v>52</v>
       </c>
       <c r="L138" s="89" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M138" s="89"/>
       <c r="N138" s="89" t="s">
         <v>53</v>
       </c>
       <c r="O138" s="94" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P138" s="95" t="s">
         <v>55</v>
@@ -22591,7 +22591,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="139" spans="1:47" ht="12" customHeight="1">
+    <row r="139" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A139" s="87" t="s">
         <v>47</v>
       </c>
@@ -22608,7 +22608,7 @@
         <v>451578210</v>
       </c>
       <c r="F139" s="220" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G139" s="92">
         <v>29336414887</v>
@@ -22626,14 +22626,14 @@
         <v>52</v>
       </c>
       <c r="L139" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M139" s="89" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="N139" s="89"/>
       <c r="O139" s="94" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P139" s="95" t="s">
         <v>55</v>
@@ -22725,7 +22725,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="140" spans="1:47" ht="12" customHeight="1">
+    <row r="140" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A140" s="87" t="s">
         <v>47</v>
       </c>
@@ -22736,16 +22736,16 @@
         <v>48</v>
       </c>
       <c r="D140" s="89" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E140" s="90">
         <v>92848596</v>
       </c>
       <c r="F140" s="220" t="s">
+        <v>404</v>
+      </c>
+      <c r="G140" s="92" t="s">
         <v>405</v>
-      </c>
-      <c r="G140" s="92" t="s">
-        <v>406</v>
       </c>
       <c r="H140" s="93">
         <v>29337</v>
@@ -22757,19 +22757,19 @@
         <v>51</v>
       </c>
       <c r="K140" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L140" s="89" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M140" s="89" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N140" s="89" t="s">
         <v>126</v>
       </c>
       <c r="O140" s="94" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="P140" s="95" t="s">
         <v>55</v>
@@ -22861,7 +22861,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="141" spans="1:47" ht="12" customHeight="1">
+    <row r="141" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A141" s="87" t="s">
         <v>47</v>
       </c>
@@ -22872,13 +22872,13 @@
         <v>48</v>
       </c>
       <c r="D141" s="89" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E141" s="90">
         <v>755343646</v>
       </c>
       <c r="F141" s="220" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G141" s="92">
         <v>65070437704</v>
@@ -22893,19 +22893,19 @@
         <v>77</v>
       </c>
       <c r="K141" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L141" s="89" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M141" s="89" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N141" s="89" t="s">
         <v>53</v>
       </c>
       <c r="O141" s="94" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P141" s="95" t="s">
         <v>55</v>
@@ -22944,7 +22944,7 @@
       </c>
       <c r="AC141" s="120"/>
       <c r="AD141" s="89" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AE141" s="89">
         <v>32</v>
@@ -23005,7 +23005,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="142" spans="1:47" ht="12" customHeight="1">
+    <row r="142" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A142" s="87" t="s">
         <v>47</v>
       </c>
@@ -23022,7 +23022,7 @@
         <v>78496696</v>
       </c>
       <c r="F142" s="220" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G142" s="92">
         <v>1791288847</v>
@@ -23137,7 +23137,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="143" spans="1:47" ht="12" customHeight="1">
+    <row r="143" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A143" s="87" t="s">
         <v>47</v>
       </c>
@@ -23148,13 +23148,13 @@
         <v>48</v>
       </c>
       <c r="D143" s="89" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E143" s="90">
         <v>450081605</v>
       </c>
       <c r="F143" s="220" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G143" s="92">
         <v>67372155800</v>
@@ -23172,10 +23172,10 @@
         <v>52</v>
       </c>
       <c r="L143" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M143" s="89" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N143" s="89" t="s">
         <v>53</v>
@@ -23275,7 +23275,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="144" spans="1:47" ht="12" customHeight="1">
+    <row r="144" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A144" s="87" t="s">
         <v>47</v>
       </c>
@@ -23292,7 +23292,7 @@
         <v>808309811</v>
       </c>
       <c r="F144" s="220" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G144" s="92">
         <v>10717308863</v>
@@ -23401,7 +23401,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="145" spans="1:47" ht="12" customHeight="1">
+    <row r="145" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A145" s="87" t="s">
         <v>47</v>
       </c>
@@ -23418,7 +23418,7 @@
         <v>596823363</v>
       </c>
       <c r="F145" s="220" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G145" s="92">
         <v>85264679800</v>
@@ -23436,7 +23436,7 @@
         <v>52</v>
       </c>
       <c r="L145" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M145" s="89"/>
       <c r="N145" s="89" t="s">
@@ -23482,7 +23482,7 @@
       </c>
       <c r="AC145" s="120"/>
       <c r="AD145" s="89" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AE145" s="89">
         <v>61</v>
@@ -23543,7 +23543,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="146" spans="1:47" ht="12" customHeight="1">
+    <row r="146" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A146" s="87" t="s">
         <v>47</v>
       </c>
@@ -23560,7 +23560,7 @@
         <v>95927283</v>
       </c>
       <c r="F146" s="220" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G146" s="92">
         <v>87215942872</v>
@@ -23578,7 +23578,7 @@
         <v>52</v>
       </c>
       <c r="L146" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M146" s="89"/>
       <c r="N146" s="89" t="s">
@@ -23628,7 +23628,7 @@
       <c r="AD146" s="89"/>
       <c r="AE146" s="89"/>
       <c r="AF146" s="99" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG146" s="99"/>
       <c r="AH146" s="99" t="s">
@@ -23694,16 +23694,16 @@
         <v>48</v>
       </c>
       <c r="D147" s="89" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E147" s="90">
         <v>451628462</v>
       </c>
       <c r="F147" s="220" t="s">
+        <v>419</v>
+      </c>
+      <c r="G147" s="92" t="s">
         <v>420</v>
-      </c>
-      <c r="G147" s="92" t="s">
-        <v>421</v>
       </c>
       <c r="H147" s="93">
         <v>12399</v>
@@ -23718,10 +23718,10 @@
         <v>52</v>
       </c>
       <c r="L147" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M147" s="89" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N147" s="89">
         <v>100</v>
@@ -23772,7 +23772,7 @@
         <v>62</v>
       </c>
       <c r="AJ147" s="100" t="s">
-        <v>264</v>
+        <v>47</v>
       </c>
       <c r="AK147" s="100" t="s">
         <v>47</v>
@@ -23817,7 +23817,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="148" spans="1:47" ht="12" customHeight="1">
+    <row r="148" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A148" s="87" t="s">
         <v>47</v>
       </c>
@@ -23828,16 +23828,16 @@
         <v>48</v>
       </c>
       <c r="D148" s="89" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E148" s="90">
         <v>76913676</v>
       </c>
       <c r="F148" s="220" t="s">
+        <v>422</v>
+      </c>
+      <c r="G148" s="92" t="s">
         <v>423</v>
-      </c>
-      <c r="G148" s="92" t="s">
-        <v>424</v>
       </c>
       <c r="H148" s="93">
         <v>23537</v>
@@ -23852,10 +23852,10 @@
         <v>52</v>
       </c>
       <c r="L148" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M148" s="89" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="N148" s="89">
         <v>50</v>
@@ -23957,7 +23957,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="149" spans="1:47" ht="12" customHeight="1">
+    <row r="149" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A149" s="87" t="s">
         <v>47</v>
       </c>
@@ -23968,16 +23968,16 @@
         <v>48</v>
       </c>
       <c r="D149" s="89" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E149" s="90">
         <v>93038167</v>
       </c>
       <c r="F149" s="220" t="s">
+        <v>425</v>
+      </c>
+      <c r="G149" s="92" t="s">
         <v>426</v>
-      </c>
-      <c r="G149" s="92" t="s">
-        <v>427</v>
       </c>
       <c r="H149" s="93">
         <v>20845</v>
@@ -23992,10 +23992,10 @@
         <v>52</v>
       </c>
       <c r="L149" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M149" s="89" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="N149" s="89">
         <v>60</v>
@@ -24087,7 +24087,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="150" spans="1:47" ht="12" customHeight="1">
+    <row r="150" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A150" s="87" t="s">
         <v>47</v>
       </c>
@@ -24104,7 +24104,7 @@
         <v>450125572</v>
       </c>
       <c r="F150" s="220" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G150" s="92">
         <v>31057896853</v>
@@ -24122,16 +24122,16 @@
         <v>52</v>
       </c>
       <c r="L150" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M150" s="89" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N150" s="89">
         <v>100</v>
       </c>
       <c r="O150" s="94" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P150" s="95" t="s">
         <v>55</v>
@@ -24231,7 +24231,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="151" spans="1:47" ht="12" customHeight="1">
+    <row r="151" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A151" s="87" t="s">
         <v>47</v>
       </c>
@@ -24248,10 +24248,10 @@
         <v>652422640</v>
       </c>
       <c r="F151" s="220" t="s">
+        <v>431</v>
+      </c>
+      <c r="G151" s="92" t="s">
         <v>432</v>
-      </c>
-      <c r="G151" s="92" t="s">
-        <v>433</v>
       </c>
       <c r="H151" s="93">
         <v>27858</v>
@@ -24357,7 +24357,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="152" spans="1:47" ht="12" customHeight="1">
+    <row r="152" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A152" s="87" t="s">
         <v>47</v>
       </c>
@@ -24374,10 +24374,10 @@
         <v>94553491</v>
       </c>
       <c r="F152" s="220" t="s">
+        <v>433</v>
+      </c>
+      <c r="G152" s="92" t="s">
         <v>434</v>
-      </c>
-      <c r="G152" s="92" t="s">
-        <v>435</v>
       </c>
       <c r="H152" s="93">
         <v>28910</v>
@@ -24495,7 +24495,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="153" spans="1:47" ht="12" customHeight="1">
+    <row r="153" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A153" s="87" t="s">
         <v>47</v>
       </c>
@@ -24506,16 +24506,16 @@
         <v>48</v>
       </c>
       <c r="D153" s="89" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E153" s="90">
         <v>592983935</v>
       </c>
       <c r="F153" s="220" t="s">
+        <v>435</v>
+      </c>
+      <c r="G153" s="92" t="s">
         <v>436</v>
-      </c>
-      <c r="G153" s="92" t="s">
-        <v>437</v>
       </c>
       <c r="H153" s="93">
         <v>23353</v>
@@ -24530,7 +24530,7 @@
         <v>52</v>
       </c>
       <c r="L153" s="89" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M153" s="89"/>
       <c r="N153" s="89">
@@ -24629,7 +24629,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="154" spans="1:47" ht="12" customHeight="1">
+    <row r="154" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A154" s="87" t="s">
         <v>47</v>
       </c>
@@ -24646,7 +24646,7 @@
         <v>72318917</v>
       </c>
       <c r="F154" s="220" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G154" s="92">
         <v>33595330706</v>
@@ -24661,17 +24661,17 @@
         <v>51</v>
       </c>
       <c r="K154" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L154" s="89" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M154" s="89"/>
       <c r="N154" s="89">
         <v>400</v>
       </c>
       <c r="O154" s="94" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P154" s="95" t="s">
         <v>55</v>
@@ -24757,7 +24757,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="155" spans="1:47" ht="12" customHeight="1">
+    <row r="155" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A155" s="87" t="s">
         <v>47</v>
       </c>
@@ -24774,7 +24774,7 @@
         <v>89717291</v>
       </c>
       <c r="F155" s="220" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G155" s="92">
         <v>36319037822</v>
@@ -24792,14 +24792,14 @@
         <v>52</v>
       </c>
       <c r="L155" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M155" s="89"/>
       <c r="N155" s="89">
         <v>450</v>
       </c>
       <c r="O155" s="94" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P155" s="95" t="s">
         <v>55</v>
@@ -24891,7 +24891,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="156" spans="1:47" ht="12" customHeight="1">
+    <row r="156" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A156" s="87" t="s">
         <v>47</v>
       </c>
@@ -24908,7 +24908,7 @@
         <v>94147640</v>
       </c>
       <c r="F156" s="220" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G156" s="92">
         <v>95453040653</v>
@@ -24923,19 +24923,19 @@
         <v>51</v>
       </c>
       <c r="K156" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L156" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M156" s="89" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="N156" s="89">
         <v>75</v>
       </c>
       <c r="O156" s="94" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="P156" s="95" t="s">
         <v>55</v>
@@ -25027,7 +25027,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="157" spans="1:47" ht="12" customHeight="1">
+    <row r="157" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A157" s="87" t="s">
         <v>47</v>
       </c>
@@ -25044,7 +25044,7 @@
         <v>95897218</v>
       </c>
       <c r="F157" s="220" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G157" s="92">
         <v>36952729372</v>
@@ -25062,16 +25062,16 @@
         <v>52</v>
       </c>
       <c r="L157" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M157" s="89" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="N157" s="89">
         <v>110</v>
       </c>
       <c r="O157" s="94" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="P157" s="95" t="s">
         <v>55</v>
@@ -25157,7 +25157,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="158" spans="1:47" ht="12" customHeight="1">
+    <row r="158" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A158" s="87" t="s">
         <v>47</v>
       </c>
@@ -25174,7 +25174,7 @@
         <v>82920071</v>
       </c>
       <c r="F158" s="220" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G158" s="92">
         <v>2746414708</v>
@@ -25189,13 +25189,13 @@
         <v>77</v>
       </c>
       <c r="K158" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L158" s="89" t="s">
+        <v>449</v>
+      </c>
+      <c r="M158" s="89" t="s">
         <v>450</v>
-      </c>
-      <c r="M158" s="89" t="s">
-        <v>451</v>
       </c>
       <c r="N158" s="89">
         <v>60</v>
@@ -25293,7 +25293,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="159" spans="1:47" ht="12" customHeight="1">
+    <row r="159" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A159" s="87" t="s">
         <v>47</v>
       </c>
@@ -25310,7 +25310,7 @@
         <v>86308398</v>
       </c>
       <c r="F159" s="220" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G159" s="92">
         <v>2214007709</v>
@@ -25325,10 +25325,10 @@
         <v>51</v>
       </c>
       <c r="K159" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L159" s="89" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M159" s="89"/>
       <c r="N159" s="89">
@@ -25427,7 +25427,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="160" spans="1:47" ht="12" customHeight="1">
+    <row r="160" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A160" s="87" t="s">
         <v>47</v>
       </c>
@@ -25444,7 +25444,7 @@
         <v>96951349</v>
       </c>
       <c r="F160" s="220" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G160" s="92">
         <v>14008427783</v>
@@ -25459,13 +25459,13 @@
         <v>51</v>
       </c>
       <c r="K160" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L160" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M160" s="89" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N160" s="89">
         <v>380</v>
@@ -25563,7 +25563,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="161" spans="1:47" ht="12" customHeight="1">
+    <row r="161" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A161" s="87" t="s">
         <v>47</v>
       </c>
@@ -25580,7 +25580,7 @@
         <v>81500877</v>
       </c>
       <c r="F161" s="220" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G161" s="92">
         <v>63054493768</v>
@@ -25598,22 +25598,22 @@
         <v>52</v>
       </c>
       <c r="L161" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M161" s="89" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N161" s="89">
         <v>60</v>
       </c>
       <c r="O161" s="94" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="P161" s="95" t="s">
         <v>55</v>
       </c>
       <c r="Q161" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R161" s="96"/>
       <c r="S161" s="97"/>
@@ -25621,7 +25621,7 @@
         <v>183</v>
       </c>
       <c r="U161" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V161" s="93">
         <v>46170</v>
@@ -25689,7 +25689,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="162" spans="1:47" ht="12" customHeight="1">
+    <row r="162" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A162" s="87" t="s">
         <v>47</v>
       </c>
@@ -25706,7 +25706,7 @@
         <v>82313899</v>
       </c>
       <c r="F162" s="220" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G162" s="92">
         <v>5279323705</v>
@@ -25721,13 +25721,13 @@
         <v>51</v>
       </c>
       <c r="K162" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L162" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M162" s="89" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N162" s="89">
         <v>60</v>
@@ -25829,7 +25829,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="163" spans="1:47" ht="12" customHeight="1">
+    <row r="163" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A163" s="87" t="s">
         <v>47</v>
       </c>
@@ -25840,16 +25840,16 @@
         <v>48</v>
       </c>
       <c r="D163" s="89" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E163" s="90">
         <v>810135647</v>
       </c>
       <c r="F163" s="220" t="s">
+        <v>460</v>
+      </c>
+      <c r="G163" s="92" t="s">
         <v>461</v>
-      </c>
-      <c r="G163" s="92" t="s">
-        <v>462</v>
       </c>
       <c r="H163" s="93">
         <v>19692</v>
@@ -25864,10 +25864,10 @@
         <v>52</v>
       </c>
       <c r="L163" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M163" s="89" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="N163" s="89">
         <v>100</v>
@@ -25879,7 +25879,7 @@
         <v>55</v>
       </c>
       <c r="Q163" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R163" s="96"/>
       <c r="S163" s="97"/>
@@ -25887,7 +25887,7 @@
         <v>183</v>
       </c>
       <c r="U163" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V163" s="93">
         <v>46170</v>
@@ -25972,7 +25972,7 @@
         <v>82246292</v>
       </c>
       <c r="F164" s="220" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G164" s="92">
         <v>25998250753</v>
@@ -25987,19 +25987,19 @@
         <v>51</v>
       </c>
       <c r="K164" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L164" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M164" s="89" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N164" s="89">
         <v>60</v>
       </c>
       <c r="O164" s="94" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P164" s="95" t="s">
         <v>55</v>
@@ -26085,7 +26085,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="165" spans="1:47" ht="12" customHeight="1">
+    <row r="165" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A165" s="87" t="s">
         <v>47</v>
       </c>
@@ -26102,7 +26102,7 @@
         <v>82246293</v>
       </c>
       <c r="F165" s="220" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G165" s="92">
         <v>38948257749</v>
@@ -26117,13 +26117,13 @@
         <v>77</v>
       </c>
       <c r="K165" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L165" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M165" s="89" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N165" s="89">
         <v>60</v>
@@ -26135,7 +26135,7 @@
         <v>55</v>
       </c>
       <c r="Q165" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R165" s="96"/>
       <c r="S165" s="97"/>
@@ -26143,7 +26143,7 @@
         <v>183</v>
       </c>
       <c r="U165" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V165" s="93">
         <v>46170</v>
@@ -26226,7 +26226,7 @@
         <v>94399117</v>
       </c>
       <c r="F166" s="220" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G166" s="92">
         <v>27126710828</v>
@@ -26244,16 +26244,16 @@
         <v>52</v>
       </c>
       <c r="L166" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M166" s="89" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N166" s="89">
         <v>60</v>
       </c>
       <c r="O166" s="94" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P166" s="95" t="s">
         <v>55</v>
@@ -26341,7 +26341,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="167" spans="1:47" ht="12" customHeight="1">
+    <row r="167" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A167" s="87" t="s">
         <v>47</v>
       </c>
@@ -26358,7 +26358,7 @@
         <v>450862801</v>
       </c>
       <c r="F167" s="220" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G167" s="92">
         <v>7690018823</v>
@@ -26376,16 +26376,16 @@
         <v>52</v>
       </c>
       <c r="L167" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M167" s="89" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="N167" s="89">
         <v>100</v>
       </c>
       <c r="O167" s="94" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P167" s="95" t="s">
         <v>55</v>
@@ -26479,7 +26479,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="168" spans="1:47" ht="12" customHeight="1">
+    <row r="168" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A168" s="87" t="s">
         <v>47</v>
       </c>
@@ -26496,7 +26496,7 @@
         <v>794141706</v>
       </c>
       <c r="F168" s="220" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G168" s="92">
         <v>7022220891</v>
@@ -26514,10 +26514,10 @@
         <v>52</v>
       </c>
       <c r="L168" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M168" s="89" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="N168" s="89" t="s">
         <v>53</v>
@@ -26529,7 +26529,7 @@
         <v>55</v>
       </c>
       <c r="Q168" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R168" s="96"/>
       <c r="S168" s="97"/>
@@ -26537,7 +26537,7 @@
         <v>183</v>
       </c>
       <c r="U168" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V168" s="93">
         <v>46170</v>
@@ -26603,7 +26603,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="169" spans="1:47" ht="12" customHeight="1">
+    <row r="169" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A169" s="87" t="s">
         <v>47</v>
       </c>
@@ -26620,7 +26620,7 @@
         <v>451984838</v>
       </c>
       <c r="F169" s="220" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G169" s="92">
         <v>25527733894</v>
@@ -26638,10 +26638,10 @@
         <v>52</v>
       </c>
       <c r="L169" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M169" s="89" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="N169" s="89">
         <v>100</v>
@@ -26653,7 +26653,7 @@
         <v>55</v>
       </c>
       <c r="Q169" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R169" s="96"/>
       <c r="S169" s="97"/>
@@ -26661,7 +26661,7 @@
         <v>183</v>
       </c>
       <c r="U169" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V169" s="93">
         <v>46170</v>
@@ -26727,7 +26727,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="170" spans="1:47" ht="12" customHeight="1">
+    <row r="170" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A170" s="87" t="s">
         <v>47</v>
       </c>
@@ -26738,16 +26738,16 @@
         <v>48</v>
       </c>
       <c r="D170" s="89" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E170" s="112">
         <v>93066193</v>
       </c>
       <c r="F170" s="220" t="s">
+        <v>477</v>
+      </c>
+      <c r="G170" s="113" t="s">
         <v>478</v>
-      </c>
-      <c r="G170" s="113" t="s">
-        <v>479</v>
       </c>
       <c r="H170" s="98">
         <v>26061</v>
@@ -26759,13 +26759,13 @@
         <v>51</v>
       </c>
       <c r="K170" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L170" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M170" s="89" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N170" s="89">
         <v>750</v>
@@ -26777,7 +26777,7 @@
         <v>55</v>
       </c>
       <c r="Q170" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R170" s="122"/>
       <c r="S170" s="97"/>
@@ -26785,7 +26785,7 @@
         <v>183</v>
       </c>
       <c r="U170" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V170" s="118">
         <v>46178</v>
@@ -26851,7 +26851,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="171" spans="1:47" ht="12" customHeight="1">
+    <row r="171" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A171" s="87" t="s">
         <v>47</v>
       </c>
@@ -26862,16 +26862,16 @@
         <v>48</v>
       </c>
       <c r="D171" s="89" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E171" s="112">
         <v>88392363</v>
       </c>
       <c r="F171" s="220" t="s">
+        <v>480</v>
+      </c>
+      <c r="G171" s="113" t="s">
         <v>481</v>
-      </c>
-      <c r="G171" s="113" t="s">
-        <v>482</v>
       </c>
       <c r="H171" s="98">
         <v>21309</v>
@@ -26886,10 +26886,10 @@
         <v>52</v>
       </c>
       <c r="L171" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M171" s="89" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N171" s="89">
         <v>380</v>
@@ -26901,7 +26901,7 @@
         <v>55</v>
       </c>
       <c r="Q171" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R171" s="122"/>
       <c r="S171" s="95"/>
@@ -26909,7 +26909,7 @@
         <v>183</v>
       </c>
       <c r="U171" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V171" s="118">
         <v>46178</v>
@@ -26977,7 +26977,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="172" spans="1:47" ht="12" customHeight="1">
+    <row r="172" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A172" s="87" t="s">
         <v>47</v>
       </c>
@@ -26988,16 +26988,16 @@
         <v>48</v>
       </c>
       <c r="D172" s="89" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E172" s="112">
         <v>96399740</v>
       </c>
       <c r="F172" s="220" t="s">
+        <v>483</v>
+      </c>
+      <c r="G172" s="113" t="s">
         <v>484</v>
-      </c>
-      <c r="G172" s="113" t="s">
-        <v>485</v>
       </c>
       <c r="H172" s="98">
         <v>20742</v>
@@ -27009,13 +27009,13 @@
         <v>51</v>
       </c>
       <c r="K172" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L172" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M172" s="89" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N172" s="89">
         <v>75</v>
@@ -27027,7 +27027,7 @@
         <v>55</v>
       </c>
       <c r="Q172" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R172" s="122"/>
       <c r="S172" s="95"/>
@@ -27035,7 +27035,7 @@
         <v>183</v>
       </c>
       <c r="U172" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V172" s="118">
         <v>46178</v>
@@ -27112,16 +27112,16 @@
         <v>48</v>
       </c>
       <c r="D173" s="89" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E173" s="112">
         <v>95660911</v>
       </c>
       <c r="F173" s="220" t="s">
+        <v>486</v>
+      </c>
+      <c r="G173" s="113" t="s">
         <v>487</v>
-      </c>
-      <c r="G173" s="113" t="s">
-        <v>488</v>
       </c>
       <c r="H173" s="98">
         <v>36599</v>
@@ -27136,10 +27136,10 @@
         <v>52</v>
       </c>
       <c r="L173" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M173" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N173" s="89">
         <v>110</v>
@@ -27231,7 +27231,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="174" spans="1:47" ht="12" customHeight="1">
+    <row r="174" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A174" s="87" t="s">
         <v>47</v>
       </c>
@@ -27239,7 +27239,7 @@
         <v>46175</v>
       </c>
       <c r="C174" s="89" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D174" s="89" t="s">
         <v>49</v>
@@ -27248,7 +27248,7 @@
         <v>759859116</v>
       </c>
       <c r="F174" s="220" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G174" s="113">
         <v>80709834772</v>
@@ -27261,25 +27261,25 @@
         <v>77</v>
       </c>
       <c r="K174" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L174" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M174" s="89" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="N174" s="89">
         <v>100</v>
       </c>
       <c r="O174" s="91" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="P174" s="95" t="s">
         <v>55</v>
       </c>
       <c r="Q174" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R174" s="122"/>
       <c r="S174" s="95"/>
@@ -27287,7 +27287,7 @@
         <v>183</v>
       </c>
       <c r="U174" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V174" s="118">
         <v>46178</v>
@@ -27361,19 +27361,19 @@
         <v>46175</v>
       </c>
       <c r="C175" s="89" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D175" s="89" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E175" s="112">
         <v>87522285</v>
       </c>
       <c r="F175" s="220" t="s">
+        <v>493</v>
+      </c>
+      <c r="G175" s="113" t="s">
         <v>494</v>
-      </c>
-      <c r="G175" s="113" t="s">
-        <v>495</v>
       </c>
       <c r="H175" s="98">
         <v>23094</v>
@@ -27383,13 +27383,13 @@
         <v>77</v>
       </c>
       <c r="K175" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L175" s="89" t="s">
+        <v>495</v>
+      </c>
+      <c r="M175" s="89" t="s">
         <v>496</v>
-      </c>
-      <c r="M175" s="89" t="s">
-        <v>497</v>
       </c>
       <c r="N175" s="89">
         <v>75</v>
@@ -27489,19 +27489,19 @@
         <v>46175</v>
       </c>
       <c r="C176" s="89" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D176" s="89" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E176" s="112">
         <v>89058286</v>
       </c>
       <c r="F176" s="220" t="s">
+        <v>497</v>
+      </c>
+      <c r="G176" s="113" t="s">
         <v>498</v>
-      </c>
-      <c r="G176" s="113" t="s">
-        <v>499</v>
       </c>
       <c r="H176" s="98">
         <v>28282</v>
@@ -27517,7 +27517,7 @@
         <v>52</v>
       </c>
       <c r="M176" s="89" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="N176" s="89">
         <v>110</v>
@@ -27609,7 +27609,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="177" spans="1:47" ht="12" customHeight="1">
+    <row r="177" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A177" s="89" t="s">
         <v>47</v>
       </c>
@@ -27617,19 +27617,19 @@
         <v>46176</v>
       </c>
       <c r="C177" s="89" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D177" s="89" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E177" s="112">
         <v>490054668</v>
       </c>
       <c r="F177" s="220" t="s">
+        <v>500</v>
+      </c>
+      <c r="G177" s="113" t="s">
         <v>501</v>
-      </c>
-      <c r="G177" s="113" t="s">
-        <v>502</v>
       </c>
       <c r="H177" s="98">
         <v>23111</v>
@@ -27639,13 +27639,13 @@
         <v>51</v>
       </c>
       <c r="K177" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L177" s="89" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M177" s="89" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="N177" s="89">
         <v>400</v>
@@ -27657,7 +27657,7 @@
         <v>55</v>
       </c>
       <c r="Q177" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R177" s="122"/>
       <c r="S177" s="95"/>
@@ -27665,7 +27665,7 @@
         <v>183</v>
       </c>
       <c r="U177" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V177" s="118">
         <v>46178</v>
@@ -27731,7 +27731,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="178" spans="1:47" ht="12" customHeight="1">
+    <row r="178" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A178" s="87" t="s">
         <v>47</v>
       </c>
@@ -27739,7 +27739,7 @@
         <v>46181</v>
       </c>
       <c r="C178" s="89" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D178" s="89" t="s">
         <v>49</v>
@@ -27748,7 +27748,7 @@
         <v>94078277</v>
       </c>
       <c r="F178" s="220" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G178" s="113">
         <v>22814062883</v>
@@ -27764,22 +27764,22 @@
         <v>52</v>
       </c>
       <c r="L178" s="89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M178" s="89" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="N178" s="89">
         <v>380</v>
       </c>
       <c r="O178" s="91" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="P178" s="95" t="s">
         <v>55</v>
       </c>
       <c r="Q178" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R178" s="122"/>
       <c r="S178" s="97"/>
@@ -27787,7 +27787,7 @@
         <v>183</v>
       </c>
       <c r="U178" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V178" s="118">
         <v>46181</v>
@@ -27859,19 +27859,19 @@
         <v>46181</v>
       </c>
       <c r="C179" s="89" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D179" s="89" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E179" s="112">
         <v>94704641</v>
       </c>
       <c r="F179" s="220" t="s">
+        <v>506</v>
+      </c>
+      <c r="G179" s="113" t="s">
         <v>507</v>
-      </c>
-      <c r="G179" s="113" t="s">
-        <v>508</v>
       </c>
       <c r="H179" s="98">
         <v>26682</v>
@@ -27881,13 +27881,13 @@
         <v>51</v>
       </c>
       <c r="K179" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L179" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M179" s="89" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="N179" s="89">
         <v>80</v>
@@ -27985,19 +27985,19 @@
         <v>46181</v>
       </c>
       <c r="C180" s="89" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D180" s="89" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E180" s="112">
         <v>92749038</v>
       </c>
       <c r="F180" s="220" t="s">
+        <v>509</v>
+      </c>
+      <c r="G180" s="113" t="s">
         <v>510</v>
-      </c>
-      <c r="G180" s="113" t="s">
-        <v>511</v>
       </c>
       <c r="H180" s="98">
         <v>19675</v>
@@ -28007,13 +28007,13 @@
         <v>51</v>
       </c>
       <c r="K180" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L180" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M180" s="89" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="N180" s="89">
         <v>75</v>
@@ -28103,7 +28103,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="181" spans="1:47" ht="12" customHeight="1">
+    <row r="181" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A181" s="87" t="s">
         <v>47</v>
       </c>
@@ -28111,19 +28111,19 @@
         <v>46181</v>
       </c>
       <c r="C181" s="89" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D181" s="89" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E181" s="112">
         <v>762342579</v>
       </c>
       <c r="F181" s="220" t="s">
+        <v>511</v>
+      </c>
+      <c r="G181" s="113" t="s">
         <v>512</v>
-      </c>
-      <c r="G181" s="113" t="s">
-        <v>513</v>
       </c>
       <c r="H181" s="98">
         <v>29274</v>
@@ -28133,13 +28133,13 @@
         <v>51</v>
       </c>
       <c r="K181" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L181" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M181" s="89" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="N181" s="89">
         <v>100</v>
@@ -28151,7 +28151,7 @@
         <v>55</v>
       </c>
       <c r="Q181" s="144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R181" s="122"/>
       <c r="S181" s="97"/>
@@ -28159,7 +28159,7 @@
         <v>183</v>
       </c>
       <c r="U181" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V181" s="118">
         <v>46181</v>
@@ -28223,7 +28223,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="182" spans="1:47" ht="12" customHeight="1">
+    <row r="182" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A182" s="87" t="s">
         <v>47</v>
       </c>
@@ -28231,19 +28231,19 @@
         <v>46182</v>
       </c>
       <c r="C182" s="89" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D182" s="89" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E182" s="112">
         <v>92604272</v>
       </c>
       <c r="F182" s="220" t="s">
+        <v>514</v>
+      </c>
+      <c r="G182" s="113" t="s">
         <v>515</v>
-      </c>
-      <c r="G182" s="113" t="s">
-        <v>516</v>
       </c>
       <c r="H182" s="98">
         <v>26168</v>
@@ -28253,13 +28253,13 @@
         <v>77</v>
       </c>
       <c r="K182" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L182" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M182" s="89" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="N182" s="89">
         <v>450</v>
@@ -28333,7 +28333,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="183" spans="1:47" ht="12" customHeight="1">
+    <row r="183" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A183" s="89" t="s">
         <v>47</v>
       </c>
@@ -28341,19 +28341,19 @@
         <v>46183</v>
       </c>
       <c r="C183" s="89" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D183" s="89" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E183" s="112">
         <v>72189038</v>
       </c>
       <c r="F183" s="220" t="s">
+        <v>517</v>
+      </c>
+      <c r="G183" s="113" t="s">
         <v>518</v>
-      </c>
-      <c r="G183" s="113" t="s">
-        <v>519</v>
       </c>
       <c r="H183" s="98">
         <v>24402</v>
@@ -28363,13 +28363,13 @@
         <v>51</v>
       </c>
       <c r="K183" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L183" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M183" s="89" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="N183" s="89">
         <v>50</v>
@@ -28443,7 +28443,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="184" spans="1:47" ht="12" customHeight="1">
+    <row r="184" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A184" s="89" t="s">
         <v>47</v>
       </c>
@@ -28451,7 +28451,7 @@
         <v>46184</v>
       </c>
       <c r="C184" s="89" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D184" s="89" t="s">
         <v>49</v>
@@ -28460,7 +28460,7 @@
         <v>84671518</v>
       </c>
       <c r="F184" s="220" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G184" s="113">
         <v>7170143712</v>
@@ -28473,13 +28473,13 @@
         <v>51</v>
       </c>
       <c r="K184" s="89" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L184" s="89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M184" s="89" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N184" s="89">
         <v>60</v>
@@ -28553,7 +28553,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="185" spans="1:47" ht="12" customHeight="1">
+    <row r="185" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A185" s="89"/>
       <c r="B185" s="93"/>
       <c r="C185" s="89"/>
@@ -28631,7 +28631,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="186" spans="1:47" ht="12" customHeight="1">
+    <row r="186" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A186" s="89"/>
       <c r="B186" s="93"/>
       <c r="C186" s="89"/>
@@ -28709,7 +28709,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="187" spans="1:47" ht="12" customHeight="1">
+    <row r="187" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A187" s="87"/>
       <c r="B187" s="93"/>
       <c r="C187" s="89"/>
@@ -28787,7 +28787,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="188" spans="1:47" ht="12" customHeight="1">
+    <row r="188" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A188" s="89"/>
       <c r="B188" s="93"/>
       <c r="C188" s="89"/>
@@ -28865,7 +28865,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="189" spans="1:47" ht="12" customHeight="1">
+    <row r="189" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A189" s="89"/>
       <c r="B189" s="93"/>
       <c r="C189" s="89"/>
@@ -28943,7 +28943,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="190" spans="1:47" ht="12" customHeight="1">
+    <row r="190" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A190" s="87"/>
       <c r="B190" s="93"/>
       <c r="C190" s="89"/>
@@ -29021,7 +29021,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="191" spans="1:47" ht="12" customHeight="1">
+    <row r="191" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A191" s="89"/>
       <c r="B191" s="93"/>
       <c r="C191" s="89"/>
@@ -29099,7 +29099,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="192" spans="1:47" ht="12" customHeight="1">
+    <row r="192" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A192" s="89"/>
       <c r="B192" s="93"/>
       <c r="C192" s="89"/>
@@ -29177,7 +29177,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="193" spans="1:47" ht="12" customHeight="1">
+    <row r="193" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A193" s="89"/>
       <c r="B193" s="93"/>
       <c r="C193" s="89"/>
@@ -29255,7 +29255,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="194" spans="1:47" ht="12" customHeight="1">
+    <row r="194" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A194" s="89"/>
       <c r="B194" s="93"/>
       <c r="C194" s="89"/>
@@ -29333,7 +29333,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="195" spans="1:47" ht="12" customHeight="1">
+    <row r="195" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A195" s="89"/>
       <c r="B195" s="93"/>
       <c r="C195" s="89"/>
@@ -29411,7 +29411,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="196" spans="1:47" ht="12" customHeight="1">
+    <row r="196" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A196" s="89"/>
       <c r="B196" s="93"/>
       <c r="C196" s="89"/>
@@ -29489,7 +29489,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="197" spans="1:47" ht="12" customHeight="1">
+    <row r="197" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A197" s="89"/>
       <c r="B197" s="93"/>
       <c r="C197" s="89"/>
@@ -29567,7 +29567,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="198" spans="1:47" ht="12" customHeight="1">
+    <row r="198" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A198" s="89"/>
       <c r="B198" s="93"/>
       <c r="C198" s="89"/>
@@ -29645,7 +29645,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="199" spans="1:47" ht="12" customHeight="1">
+    <row r="199" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A199" s="89"/>
       <c r="B199" s="93"/>
       <c r="C199" s="89"/>
@@ -29723,7 +29723,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="200" spans="1:47" ht="12" customHeight="1">
+    <row r="200" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A200" s="89"/>
       <c r="B200" s="93"/>
       <c r="C200" s="89"/>
@@ -29801,7 +29801,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="201" spans="1:47" ht="12" customHeight="1">
+    <row r="201" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A201" s="89"/>
       <c r="B201" s="93"/>
       <c r="C201" s="89"/>
@@ -29879,7 +29879,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="202" spans="1:47" ht="12" customHeight="1">
+    <row r="202" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A202" s="89"/>
       <c r="B202" s="93"/>
       <c r="C202" s="89"/>
@@ -29957,7 +29957,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="203" spans="1:47" ht="12" customHeight="1">
+    <row r="203" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A203" s="89"/>
       <c r="B203" s="93"/>
       <c r="C203" s="89"/>
@@ -30035,7 +30035,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="204" spans="1:47" ht="12" customHeight="1">
+    <row r="204" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A204" s="89"/>
       <c r="B204" s="93"/>
       <c r="C204" s="89"/>
@@ -30113,7 +30113,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="205" spans="1:47" ht="12" customHeight="1">
+    <row r="205" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A205" s="89"/>
       <c r="B205" s="93"/>
       <c r="C205" s="89"/>
@@ -30191,7 +30191,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="206" spans="1:47" ht="12" customHeight="1">
+    <row r="206" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A206" s="89"/>
       <c r="B206" s="93"/>
       <c r="C206" s="89"/>
@@ -30269,7 +30269,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="207" spans="1:47" ht="12" customHeight="1">
+    <row r="207" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A207" s="89"/>
       <c r="B207" s="93"/>
       <c r="C207" s="89"/>
@@ -30347,7 +30347,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="208" spans="1:47" ht="12" customHeight="1">
+    <row r="208" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A208" s="89"/>
       <c r="B208" s="93"/>
       <c r="C208" s="89"/>
@@ -30425,7 +30425,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="209" spans="1:47" ht="12" customHeight="1">
+    <row r="209" spans="1:47" ht="12" hidden="1" customHeight="1">
       <c r="A209" s="89"/>
       <c r="B209" s="93"/>
       <c r="C209" s="89"/>
@@ -63761,7 +63761,18 @@
       <c r="AU6867" s="45"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AU209" xr:uid="{9931A248-8A11-4D8E-BACD-A0C0D59E4D18}"/>
+  <autoFilter ref="A1:AU209" xr:uid="{9931A248-8A11-4D8E-BACD-A0C0D59E4D18}">
+    <filterColumn colId="16">
+      <filters>
+        <filter val="1. Aceitou o programa"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="17">
+      <filters>
+        <dateGroupItem year="2026" month="6" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="A1:A568">
     <cfRule type="containsText" dxfId="27" priority="5" operator="containsText" text="Sim">
       <formula>NOT(ISERROR(SEARCH("Sim",A1)))</formula>
@@ -63976,10 +63987,10 @@
     </row>
     <row r="4" spans="1:31" hidden="1">
       <c r="B4" s="210" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4" s="81" t="s">
         <v>523</v>
-      </c>
-      <c r="C4" s="81" t="s">
-        <v>524</v>
       </c>
       <c r="F4" s="40"/>
     </row>
@@ -63997,13 +64008,13 @@
         <v>46143</v>
       </c>
       <c r="D7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8" spans="1:31" hidden="1"/>
     <row r="9" spans="1:31" hidden="1">
       <c r="B9" s="212" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C9" s="78">
         <v>46023</v>
@@ -64011,7 +64022,7 @@
     </row>
     <row r="10" spans="1:31" hidden="1">
       <c r="B10" s="212" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C10" s="78">
         <v>46165</v>
@@ -64021,7 +64032,7 @@
     <row r="12" spans="1:31" s="218" customFormat="1">
       <c r="A12" s="216"/>
       <c r="B12" s="217" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C12" s="216"/>
       <c r="D12" s="216"/>
@@ -64065,11 +64076,11 @@
       <c r="F14" s="175"/>
       <c r="G14" s="175"/>
       <c r="H14" s="175" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I14" s="175"/>
       <c r="K14" s="236" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L14" s="175" t="s">
         <v>39</v>
@@ -64083,13 +64094,13 @@
         <v>16</v>
       </c>
       <c r="T14" s="77" t="s">
+        <v>530</v>
+      </c>
+      <c r="U14" s="77" t="s">
         <v>531</v>
       </c>
-      <c r="U14" s="77" t="s">
-        <v>532</v>
-      </c>
       <c r="W14" s="185" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="X14" s="185"/>
       <c r="Y14" s="185"/>
@@ -64112,10 +64123,10 @@
         <v>5</v>
       </c>
       <c r="H15" s="175" t="s">
+        <v>530</v>
+      </c>
+      <c r="I15" s="175" t="s">
         <v>531</v>
-      </c>
-      <c r="I15" s="175" t="s">
-        <v>532</v>
       </c>
       <c r="K15" s="236"/>
       <c r="L15" s="176">
@@ -64134,7 +64145,7 @@
         <v>5</v>
       </c>
       <c r="Q15" s="175" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="S15" s="192" t="s">
         <v>70</v>
@@ -64148,7 +64159,7 @@
         <v>0.6586826347305389</v>
       </c>
       <c r="W15" s="186" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="X15" s="186"/>
       <c r="Y15" s="187">
@@ -64189,7 +64200,7 @@
         <v>0.52380952380952384</v>
       </c>
       <c r="K16" s="36" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L16" s="36">
         <f t="shared" ref="L16:Q16" si="2">+C41</f>
@@ -64216,7 +64227,7 @@
         <v>21</v>
       </c>
       <c r="S16" s="205" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="T16" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S16,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64227,7 +64238,7 @@
         <v>0</v>
       </c>
       <c r="W16" s="207" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="X16" s="207"/>
       <c r="Y16" s="209">
@@ -64237,7 +64248,7 @@
     </row>
     <row r="17" spans="2:25">
       <c r="B17" s="194" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C17" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B17,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64295,7 +64306,7 @@
         <v>11</v>
       </c>
       <c r="S17" s="192" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T17" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S17,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64306,7 +64317,7 @@
         <v>0</v>
       </c>
       <c r="W17" s="186" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="X17" s="186"/>
       <c r="Y17" s="188">
@@ -64316,7 +64327,7 @@
     </row>
     <row r="18" spans="2:25">
       <c r="B18" s="193" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C18" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B18,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64347,7 +64358,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="193" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L18" s="41" t="str">
         <f t="shared" ref="L18:Q18" si="5">IFERROR(L17/L16,"")</f>
@@ -64374,7 +64385,7 @@
         <v>0.52380952380952384</v>
       </c>
       <c r="S18" s="205" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="T18" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S18,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64385,7 +64396,7 @@
         <v>0</v>
       </c>
       <c r="W18" s="207" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="X18" s="207"/>
       <c r="Y18" s="209">
@@ -64395,7 +64406,7 @@
     </row>
     <row r="19" spans="2:25">
       <c r="B19" s="194" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C19" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B19,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64426,7 +64437,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="194" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L19" s="177">
         <f>IFERROR(SUMIFS(Consolidado!$AQ:$AQ,Consolidado!$AN:$AN,Análise!L15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3))/L$17,0)</f>
@@ -64453,7 +64464,7 @@
         <v>9.8181818181818183</v>
       </c>
       <c r="S19" s="192" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="T19" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S19,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64464,7 +64475,7 @@
         <v>0</v>
       </c>
       <c r="W19" s="186" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="X19" s="186"/>
       <c r="Y19" s="188">
@@ -64474,7 +64485,7 @@
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="193" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C20" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B20,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64505,7 +64516,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="193" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L20" s="178">
         <f>IFERROR(SUMIFS(Consolidado!$AS:$AS,Consolidado!$AN:$AN,Análise!L15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3))/COUNTIFS(Consolidado!$AN:$AN,Análise!L15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,$K17,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AS:$AS,"&lt;&gt;"&amp;0),0)</f>
@@ -64532,7 +64543,7 @@
         <v>7.166666666666667</v>
       </c>
       <c r="S20" s="205" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="T20" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S20,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64543,7 +64554,7 @@
         <v>0</v>
       </c>
       <c r="W20" s="207" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="X20" s="207"/>
       <c r="Y20" s="208">
@@ -64553,7 +64564,7 @@
     </row>
     <row r="21" spans="2:25">
       <c r="B21" s="194" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C21" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B21,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64584,7 +64595,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="194" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="L21" s="177">
         <f>IFERROR(SUMIFS(Consolidado!$AT:$AT,Consolidado!$AN:$AN,Análise!L15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3))/COUNTIFS(Consolidado!$AN:$AN,Análise!L15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,$K17,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AT:$AT,"&lt;&gt;"&amp;0),0)</f>
@@ -64611,7 +64622,7 @@
         <v>8</v>
       </c>
       <c r="S21" s="192" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="T21" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S21,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64624,7 +64635,7 @@
     </row>
     <row r="22" spans="2:25">
       <c r="B22" s="193" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C22" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B22,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64655,7 +64666,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="205" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="T22" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S22,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64666,18 +64677,18 @@
         <v>0</v>
       </c>
       <c r="W22" s="77" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="X22" s="77" t="s">
+        <v>530</v>
+      </c>
+      <c r="Y22" s="77" t="s">
         <v>531</v>
-      </c>
-      <c r="Y22" s="77" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="23" spans="2:25">
       <c r="B23" s="194" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C23" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B23,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64708,7 +64719,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="192" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="T23" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S23,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64732,7 +64743,7 @@
     </row>
     <row r="24" spans="2:25">
       <c r="B24" s="193" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C24" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B24,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64763,7 +64774,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="236" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L24" s="175" t="s">
         <v>39</v>
@@ -64774,7 +64785,7 @@
       <c r="P24" s="175"/>
       <c r="Q24" s="175"/>
       <c r="S24" s="205" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T24" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S24,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64798,7 +64809,7 @@
     </row>
     <row r="25" spans="2:25">
       <c r="B25" s="194" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C25" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B25,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64845,10 +64856,10 @@
         <v>5</v>
       </c>
       <c r="Q25" s="175" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="S25" s="192" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="T25" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S25,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64861,7 +64872,7 @@
     </row>
     <row r="26" spans="2:25">
       <c r="B26" s="193" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C26" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B26,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64892,7 +64903,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="36" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L26" s="75">
         <f>IFERROR(SUMIFS(Consolidado!AR:AR,Consolidado!$AN:$AN,L25,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3))/COUNTIFS(Consolidado!$R:$R,"&lt;&gt;",Consolidado!$S:$S,"&lt;&gt;",Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AN:$AN,L25),0)</f>
@@ -64919,7 +64930,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="205" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="T26" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S26,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64932,7 +64943,7 @@
     </row>
     <row r="27" spans="2:25">
       <c r="B27" s="194" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C27" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B27,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64963,7 +64974,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="192" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="T27" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S27,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64976,7 +64987,7 @@
     </row>
     <row r="28" spans="2:25">
       <c r="B28" s="193" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C28" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B28,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65051,7 +65062,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="236" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L29" s="175" t="s">
         <v>39</v>
@@ -65062,7 +65073,7 @@
       <c r="P29" s="175"/>
       <c r="Q29" s="175"/>
       <c r="S29" s="192" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T29" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S29,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65075,7 +65086,7 @@
     </row>
     <row r="30" spans="2:25">
       <c r="B30" s="193" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C30" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B30,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65122,10 +65133,10 @@
         <v>5</v>
       </c>
       <c r="Q30" s="175" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="S30" s="205" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="T30" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S30,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65138,7 +65149,7 @@
     </row>
     <row r="31" spans="2:25">
       <c r="B31" s="194" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C31" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B31,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65169,7 +65180,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L31" s="182" t="str">
         <f t="shared" ref="L31:Q31" si="6">IFERROR((C16+C38)/C41,"")</f>
@@ -65196,7 +65207,7 @@
         <v>0.90476190476190477</v>
       </c>
       <c r="S31" s="192" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="T31" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S31,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65209,7 +65220,7 @@
     </row>
     <row r="32" spans="2:25">
       <c r="B32" s="193" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C32" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B32,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65240,7 +65251,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="205" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="T32" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S32,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65253,7 +65264,7 @@
     </row>
     <row r="33" spans="1:31">
       <c r="B33" s="194" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C33" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B33,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65284,7 +65295,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="192" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="T33" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S33,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65297,7 +65308,7 @@
     </row>
     <row r="34" spans="1:31">
       <c r="B34" s="193" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C34" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B34,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65328,16 +65339,16 @@
         <v>0</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L34" s="37" t="s">
+        <v>530</v>
+      </c>
+      <c r="M34" s="175" t="s">
         <v>531</v>
       </c>
-      <c r="M34" s="175" t="s">
-        <v>532</v>
-      </c>
       <c r="S34" s="205" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="T34" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S34,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65350,7 +65361,7 @@
     </row>
     <row r="35" spans="1:31">
       <c r="B35" s="194" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C35" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B35,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65392,7 +65403,7 @@
         <v>0.18181818181818182</v>
       </c>
       <c r="S35" s="192" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="T35" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S35,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65405,7 +65416,7 @@
     </row>
     <row r="36" spans="1:31">
       <c r="B36" s="193" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C36" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B36,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65491,7 +65502,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
       <c r="S37" s="192" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T37" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S37,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65504,7 +65515,7 @@
     </row>
     <row r="38" spans="1:31">
       <c r="B38" s="193" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C38" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B38,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65535,7 +65546,7 @@
         <v>0.38095238095238093</v>
       </c>
       <c r="S38" s="205" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="T38" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S38,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65548,7 +65559,7 @@
     </row>
     <row r="39" spans="1:31">
       <c r="B39" s="194" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C39" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B39,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65579,7 +65590,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="192" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="T39" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S39,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65592,7 +65603,7 @@
     </row>
     <row r="40" spans="1:31">
       <c r="B40" s="193" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C40" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B40,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65623,7 +65634,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="206" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T40" s="39">
         <f>SUM(T15:T39)</f>
@@ -65636,7 +65647,7 @@
     </row>
     <row r="41" spans="1:31">
       <c r="B41" s="39" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C41" s="39">
         <f t="shared" ref="C41:H41" si="7">SUM(C16:C40)</f>
@@ -65670,7 +65681,7 @@
     <row r="43" spans="1:31" s="218" customFormat="1">
       <c r="A43" s="216"/>
       <c r="B43" s="217" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C43" s="216"/>
       <c r="D43" s="216"/>
@@ -65714,7 +65725,7 @@
       <c r="F45" s="175"/>
       <c r="G45" s="175"/>
       <c r="H45" s="237" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="46" spans="1:31">
@@ -65770,7 +65781,7 @@
         <v>16</v>
       </c>
       <c r="C49" s="77" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="50" spans="1:31">
@@ -65785,7 +65796,7 @@
     <row r="52" spans="1:31" s="218" customFormat="1">
       <c r="A52" s="216"/>
       <c r="B52" s="217" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C52" s="216"/>
       <c r="D52" s="216"/>
@@ -65819,7 +65830,7 @@
     </row>
     <row r="54" spans="1:31">
       <c r="B54" s="232" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C54" s="175" t="s">
         <v>39</v>
@@ -65830,10 +65841,10 @@
       <c r="G54" s="175"/>
       <c r="H54" s="175"/>
       <c r="K54" s="233" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L54" s="234" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="55" spans="1:31">
@@ -65854,14 +65865,14 @@
         <v>5</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K55" s="233"/>
       <c r="L55" s="235"/>
     </row>
     <row r="56" spans="1:31">
       <c r="B56" s="47" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C56" s="36">
         <f>COUNTIFS(Consolidado!$AF:$AF,$B56,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$55,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -65888,7 +65899,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="203" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L56" s="79">
         <f>COUNTIFS(Consolidado!$AF:$AF,$K56,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -65897,7 +65908,7 @@
     </row>
     <row r="57" spans="1:31">
       <c r="B57" s="48" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C57" s="38">
         <f>COUNTIFS(Consolidado!$AF:$AF,$B57,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$55,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -65924,7 +65935,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="48" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L57" s="38">
         <f>COUNTIFS(Consolidado!$AF:$AF,$K57,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -65933,7 +65944,7 @@
     </row>
     <row r="58" spans="1:31">
       <c r="B58" s="47" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C58" s="36">
         <f>COUNTIFS(Consolidado!$AF:$AF,$B58,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$55,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -65960,7 +65971,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="203" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L58" s="79">
         <f>COUNTIFS(Consolidado!$AF:$AF,$K58,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -66005,7 +66016,7 @@
     </row>
     <row r="60" spans="1:31">
       <c r="B60" s="47" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C60" s="36">
         <f>COUNTIFS(Consolidado!$AF:$AF,$B60,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$55,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -66032,7 +66043,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="203" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L60" s="79">
         <f>COUNTIFS(Consolidado!$AF:$AF,$K60,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -66077,7 +66088,7 @@
     </row>
     <row r="62" spans="1:31">
       <c r="B62" s="47" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C62" s="44">
         <f>SUM(C56:C61)</f>
@@ -66104,7 +66115,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="203" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L62" s="204">
         <f>SUM(L56:L61)</f>
@@ -66113,7 +66124,7 @@
     </row>
     <row r="64" spans="1:31">
       <c r="B64" s="232" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C64" s="175" t="s">
         <v>39</v>
@@ -66124,10 +66135,10 @@
       <c r="G64" s="175"/>
       <c r="H64" s="175"/>
       <c r="K64" s="233" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L64" s="234" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="65" spans="1:31">
@@ -66148,14 +66159,14 @@
         <v>5</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K65" s="233"/>
       <c r="L65" s="235"/>
     </row>
     <row r="66" spans="1:31">
       <c r="B66" s="47" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C66" s="41" t="str">
         <f>IFERROR(COUNTIFS(Consolidado!$AG:$AG,$B66,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$65,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AF:$AF,"&lt;&gt;",Consolidado!$AF:$AF,"&lt;&gt;"&amp;$B66,Consolidado!$AU:$AU,"S")/(C$59+C$60+C$61),"")</f>
@@ -66182,7 +66193,7 @@
         <v/>
       </c>
       <c r="K66" s="203" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L66" s="80">
         <f>IFERROR(COUNTIFS(Consolidado!$AG:$AG,$K66,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AF:$AF,"&lt;&gt;",Consolidado!$AF:$AF,"&lt;&gt;"&amp;$K66,Consolidado!$AU:$AU,"S")/(L$59+L$60+L$61),"")</f>
@@ -66191,7 +66202,7 @@
     </row>
     <row r="67" spans="1:31">
       <c r="B67" s="48" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C67" s="42" t="str">
         <f>IFERROR(COUNTIFS(Consolidado!$AG:$AG,$B67,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$65,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AF:$AF,"&lt;&gt;",Consolidado!$AF:$AF,"&lt;&gt;"&amp;$B67,Consolidado!$AU:$AU,"S")/(C$59+C$60+C$61),"")</f>
@@ -66218,7 +66229,7 @@
         <v/>
       </c>
       <c r="K67" s="48" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L67" s="42">
         <f>IFERROR(COUNTIFS(Consolidado!$AG:$AG,$K67,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AF:$AF,"&lt;&gt;",Consolidado!$AF:$AF,"&lt;&gt;"&amp;$K67,Consolidado!$AU:$AU,"S")/(L$59+L$60+L$61),"")</f>
@@ -66227,7 +66238,7 @@
     </row>
     <row r="68" spans="1:31">
       <c r="B68" s="47" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C68" s="41" t="str">
         <f>IFERROR(COUNTIFS(Consolidado!$AG:$AG,$B68,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$65,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AF:$AF,"&lt;&gt;",Consolidado!$AF:$AF,"&lt;&gt;"&amp;$B68,Consolidado!$AU:$AU,"S")/(C$59+C$60+C$61),"")</f>
@@ -66254,7 +66265,7 @@
         <v/>
       </c>
       <c r="K68" s="203" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L68" s="80">
         <f>IFERROR(COUNTIFS(Consolidado!$AG:$AG,$K68,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AF:$AF,"&lt;&gt;",Consolidado!$AF:$AF,"&lt;&gt;"&amp;$K68,Consolidado!$AU:$AU,"S")/(L$59+L$60+L$61),"")</f>
@@ -66264,7 +66275,7 @@
     <row r="70" spans="1:31" s="218" customFormat="1">
       <c r="A70" s="216"/>
       <c r="B70" s="217" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C70" s="216"/>
       <c r="D70" s="216"/>
@@ -66298,7 +66309,7 @@
     </row>
     <row r="72" spans="1:31">
       <c r="B72" s="35" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C72" s="46">
         <v>1</v>
@@ -66316,18 +66327,18 @@
         <v>5</v>
       </c>
       <c r="H72" s="46" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K72" s="76" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="L72" s="213" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="73" spans="1:31">
       <c r="B73" s="47" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C73" s="36">
         <f>COUNTIFS(Consolidado!$AH:$AH,$B73,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$55,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -66354,7 +66365,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="203" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="L73" s="79">
         <f>COUNTIFS(Consolidado!$AH:$AH,$B73,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -66435,7 +66446,7 @@
     </row>
     <row r="76" spans="1:31">
       <c r="B76" s="48" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C76" s="39">
         <f>SUM(C73:C75)</f>
@@ -66462,7 +66473,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="48" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L76" s="39">
         <f>SUM(L73:L75)</f>
@@ -66471,28 +66482,28 @@
     </row>
     <row r="78" spans="1:31">
       <c r="B78" s="35" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C78" s="46" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K78" s="76" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L78" s="213" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="79" spans="1:31">
       <c r="B79" s="47" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C79" s="49" t="str">
         <f>IFERROR(H73/$H$76,"")</f>
         <v/>
       </c>
       <c r="K79" s="203" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="L79" s="214">
         <f>IFERROR(L73/$L$76,"")</f>
@@ -66534,7 +66545,7 @@
     <row r="83" spans="1:31" s="218" customFormat="1">
       <c r="A83" s="216"/>
       <c r="B83" s="217" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C83" s="216"/>
       <c r="D83" s="216"/>
@@ -66568,7 +66579,7 @@
     </row>
     <row r="85" spans="1:31">
       <c r="B85" s="35" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C85" s="46">
         <v>1</v>
@@ -66586,13 +66597,13 @@
         <v>5</v>
       </c>
       <c r="H85" s="46" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K85" s="76" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L85" s="213" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="86" spans="1:31">
@@ -66633,7 +66644,7 @@
     </row>
     <row r="87" spans="1:31">
       <c r="B87" s="48" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C87" s="38">
         <f>COUNTIFS(Consolidado!$Z:$Z,$B87,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$55,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -66660,7 +66671,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="48" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L87" s="38">
         <f>COUNTIFS(Consolidado!$Z:$Z,$B87,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -66669,7 +66680,7 @@
     </row>
     <row r="88" spans="1:31">
       <c r="B88" s="47" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C88" s="36">
         <f>COUNTIFS(Consolidado!$Z:$Z,$B88,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$55,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -66696,7 +66707,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="203" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="L88" s="79">
         <f>COUNTIFS(Consolidado!$Z:$Z,$B88,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -66705,7 +66716,7 @@
     </row>
     <row r="89" spans="1:31">
       <c r="B89" s="48" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C89" s="39">
         <f>SUM(C86:C88)</f>
@@ -66732,7 +66743,7 @@
         <v>12</v>
       </c>
       <c r="K89" s="48" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L89" s="39">
         <f>SUM(L86:L88)</f>
@@ -66741,7 +66752,7 @@
     </row>
     <row r="91" spans="1:31">
       <c r="B91" s="35" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C91" s="46">
         <v>1</v>
@@ -66759,13 +66770,13 @@
         <v>5</v>
       </c>
       <c r="H91" s="46" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K91" s="76" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L91" s="213" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="92" spans="1:31">
@@ -66842,7 +66853,7 @@
     </row>
     <row r="94" spans="1:31">
       <c r="B94" s="47" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C94" s="36">
         <f>COUNTIFS(Consolidado!$AB:$AB,$B94,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$91,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Z:$Z,"Agendada",Consolidado!$AU:$AU,"S")</f>
@@ -66869,7 +66880,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="203" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="L94" s="79">
         <f>COUNTIFS(Consolidado!$AB:$AB,$B94,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Z:$Z,"Agendada",Consolidado!$AU:$AU,"S")</f>
@@ -66914,7 +66925,7 @@
     </row>
     <row r="96" spans="1:31">
       <c r="B96" s="47" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C96" s="36">
         <f>COUNTIFS(Consolidado!$AB:$AB,$B96,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$91,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Z:$Z,"Agendada",Consolidado!$AU:$AU,"S")</f>
@@ -66941,7 +66952,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="203" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="L96" s="79">
         <f>COUNTIFS(Consolidado!$AB:$AB,$B96,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Z:$Z,"Agendada",Consolidado!$AU:$AU,"S")</f>
@@ -66950,7 +66961,7 @@
     </row>
     <row r="97" spans="1:31">
       <c r="B97" s="48" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C97" s="38">
         <f>COUNTIFS(Consolidado!$AB:$AB,$B97,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$91,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Z:$Z,"Agendada",Consolidado!$AU:$AU,"S")</f>
@@ -66977,7 +66988,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="48" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="L97" s="38">
         <f>COUNTIFS(Consolidado!$AB:$AB,$B97,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Z:$Z,"Agendada",Consolidado!$AU:$AU,"S")</f>
@@ -66986,7 +66997,7 @@
     </row>
     <row r="98" spans="1:31">
       <c r="B98" s="47" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C98" s="44">
         <f t="shared" ref="C98:H98" si="14">SUM(C92:C97)</f>
@@ -67013,7 +67024,7 @@
         <v>9</v>
       </c>
       <c r="K98" s="203" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L98" s="204">
         <f>SUM(L92:L97)</f>
@@ -67023,7 +67034,7 @@
     <row r="100" spans="1:31" s="218" customFormat="1">
       <c r="A100" s="216"/>
       <c r="B100" s="217" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C100" s="216"/>
       <c r="D100" s="216"/>
@@ -67075,7 +67086,7 @@
         <v>3</v>
       </c>
       <c r="L102" s="234" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="103" spans="1:31">
@@ -67096,7 +67107,7 @@
         <v>5</v>
       </c>
       <c r="H103" s="37" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K103" s="233"/>
       <c r="L103" s="235"/>
@@ -67139,7 +67150,7 @@
     </row>
     <row r="105" spans="1:31">
       <c r="B105" s="48" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C105" s="38">
         <f>COUNTIFS(Consolidado!$D:$D,$B105,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$103,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -67166,7 +67177,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="48" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="L105" s="38">
         <f>COUNTIFS(Consolidado!$D:$D,$K105,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -67175,7 +67186,7 @@
     </row>
     <row r="106" spans="1:31">
       <c r="B106" s="47" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C106" s="36">
         <f>COUNTIFS(Consolidado!$D:$D,$B106,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$103,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -67202,7 +67213,7 @@
         <v>6</v>
       </c>
       <c r="K106" s="203" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L106" s="79">
         <f>COUNTIFS(Consolidado!$D:$D,$K106,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -67211,7 +67222,7 @@
     </row>
     <row r="107" spans="1:31">
       <c r="B107" s="48" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C107" s="38">
         <f>COUNTIFS(Consolidado!$D:$D,$B107,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$103,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -67238,7 +67249,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="48" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="L107" s="38">
         <f>COUNTIFS(Consolidado!$D:$D,$K107,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -67247,7 +67258,7 @@
     </row>
     <row r="108" spans="1:31">
       <c r="B108" s="47" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C108" s="36">
         <f>COUNTIFS(Consolidado!$D:$D,$B108,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$103,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -67274,7 +67285,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="203" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L108" s="79">
         <f>COUNTIFS(Consolidado!$D:$D,$K108,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -67283,7 +67294,7 @@
     </row>
     <row r="109" spans="1:31">
       <c r="B109" s="48" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C109" s="38">
         <f>COUNTIFS(Consolidado!$D:$D,$B109,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$103,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -67310,7 +67321,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="48" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="L109" s="38">
         <f>COUNTIFS(Consolidado!$D:$D,$K109,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -67319,7 +67330,7 @@
     </row>
     <row r="110" spans="1:31">
       <c r="B110" s="47" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C110" s="36">
         <f>COUNTIFS(Consolidado!$D:$D,$B110,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$103,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -67346,7 +67357,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="203" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="L110" s="79">
         <f>COUNTIFS(Consolidado!$D:$D,$K110,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -67355,7 +67366,7 @@
     </row>
     <row r="111" spans="1:31">
       <c r="B111" s="48" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C111" s="39">
         <f>SUM(C104:C110)</f>
@@ -67382,7 +67393,7 @@
         <v>21</v>
       </c>
       <c r="K111" s="48" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L111" s="39">
         <f>SUM(L104:L110)</f>
@@ -67490,33 +67501,33 @@
         <v>2</v>
       </c>
       <c r="F1" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G1" s="53"/>
       <c r="H1" s="154" t="s">
         <v>37</v>
       </c>
       <c r="I1" s="153" t="s">
+        <v>587</v>
+      </c>
+      <c r="K1" s="71" t="s">
         <v>588</v>
-      </c>
-      <c r="K1" s="71" t="s">
-        <v>589</v>
       </c>
       <c r="L1" s="53"/>
       <c r="M1" s="54" t="s">
         <v>37</v>
       </c>
       <c r="N1" s="55" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P1" s="157" t="s">
         <v>32</v>
       </c>
       <c r="R1" s="56" t="s">
+        <v>590</v>
+      </c>
+      <c r="T1" s="74" t="s">
         <v>591</v>
-      </c>
-      <c r="T1" s="74" t="s">
-        <v>592</v>
       </c>
       <c r="V1" s="169" t="s">
         <v>16</v>
@@ -67537,7 +67548,7 @@
         <v>29</v>
       </c>
       <c r="AH1" s="160" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AJ1" s="161" t="s">
         <v>35</v>
@@ -67551,17 +67562,17 @@
     </row>
     <row r="2" spans="2:40" ht="15" thickBot="1">
       <c r="B2" s="52" t="s">
+        <v>593</v>
+      </c>
+      <c r="D2" s="147" t="s">
         <v>594</v>
-      </c>
-      <c r="D2" s="147" t="s">
-        <v>595</v>
       </c>
       <c r="F2" s="70" t="str" cm="1">
         <f t="array" ref="F2:F10">IF(COUNTIF(Consolidado!$AL:$AL,"Emagrecimento")&lt;&gt;0,_xlfn._xlws.FILTER($I$2:$I$54,$H$2:$H$54&lt;&gt;""),_xlfn._xlws.FILTER($I$2:$I$54,$H$2:$H$54="Outras"))</f>
         <v>Captado pela Amil/Call Center</v>
       </c>
       <c r="H2" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I2" s="149" t="s">
         <v>49</v>
@@ -67571,19 +67582,19 @@
         <v>Amil Paulistano</v>
       </c>
       <c r="M2" s="79" t="s">
+        <v>595</v>
+      </c>
+      <c r="N2" s="150" t="s">
+        <v>378</v>
+      </c>
+      <c r="P2" s="158" t="s">
+        <v>378</v>
+      </c>
+      <c r="R2" s="59" t="s">
         <v>596</v>
       </c>
-      <c r="N2" s="150" t="s">
-        <v>379</v>
-      </c>
-      <c r="P2" s="158" t="s">
-        <v>379</v>
-      </c>
-      <c r="R2" s="59" t="s">
-        <v>597</v>
-      </c>
       <c r="T2" s="85" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="V2" s="170" t="s">
         <v>70</v>
@@ -67624,40 +67635,40 @@
         <v>Casos Prioritário - E-mail</v>
       </c>
       <c r="H3" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I3" s="149" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="K3" s="60" t="str">
         <v>Samaritano Higi</v>
       </c>
       <c r="M3" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N3" s="150" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="P3" s="158" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="R3" s="59" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="T3" s="84" t="s">
         <v>75</v>
       </c>
       <c r="V3" s="170" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="X3" s="147" t="s">
         <v>183</v>
       </c>
       <c r="Z3" s="147" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AB3" s="166" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AD3" s="158" t="s">
         <v>118</v>
@@ -67686,47 +67697,47 @@
         <v>Forms Total Care</v>
       </c>
       <c r="H4" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I4" s="149" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K4" s="60" t="str">
         <v>COI -RJ</v>
       </c>
       <c r="M4" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N4" s="150" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="P4" s="158" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="R4" s="59" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="T4" s="84" t="s">
         <v>236</v>
       </c>
       <c r="V4" s="170" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="X4" s="166" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="Z4" s="59" t="s">
         <v>58</v>
       </c>
       <c r="AD4" s="158" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AF4" s="164" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AH4" s="159"/>
       <c r="AJ4" s="159" t="s">
-        <v>264</v>
+        <v>601</v>
       </c>
       <c r="AL4" s="158" t="s">
         <v>602</v>
@@ -67741,16 +67752,16 @@
         <v>GSC</v>
       </c>
       <c r="H5" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I5" s="149" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="K5" s="60" t="str">
         <v>Interno - Amil Geral</v>
       </c>
       <c r="M5" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N5" s="150" t="s">
         <v>100</v>
@@ -67765,7 +67776,7 @@
         <v>602</v>
       </c>
       <c r="V5" s="170" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Z5" s="59"/>
       <c r="AD5" s="158" t="s">
@@ -67786,29 +67797,29 @@
         <v>Triggers</v>
       </c>
       <c r="H6" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I6" s="149" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="K6" s="60" t="str">
         <v>Externo - Geral</v>
       </c>
       <c r="M6" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N6" s="150" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="R6" s="59" t="s">
         <v>607</v>
       </c>
       <c r="V6" s="170" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="Z6" s="224"/>
       <c r="AD6" s="159" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AF6" s="83"/>
       <c r="AH6" s="83"/>
@@ -67821,16 +67832,16 @@
         <v xml:space="preserve">Viva Bem </v>
       </c>
       <c r="H7" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I7" s="149" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K7" s="60" t="str">
         <v>Não Informou</v>
       </c>
       <c r="M7" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N7" s="150" t="s">
         <v>74</v>
@@ -67839,7 +67850,7 @@
         <v>608</v>
       </c>
       <c r="V7" s="170" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AD7" s="83"/>
       <c r="AF7" s="83"/>
@@ -67853,16 +67864,16 @@
         <v>Saúde Ocupacional</v>
       </c>
       <c r="H8" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I8" s="149" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="K8" s="60" t="str">
         <v>CMDP - Centro Médico Dom Pedro</v>
       </c>
       <c r="M8" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N8" s="150" t="s">
         <v>609</v>
@@ -67871,7 +67882,7 @@
         <v>610</v>
       </c>
       <c r="V8" s="170" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AD8" s="83"/>
       <c r="AF8" s="83"/>
@@ -67894,7 +67905,7 @@
         <v>Outros</v>
       </c>
       <c r="M9" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N9" s="150" t="s">
         <v>613</v>
@@ -67903,7 +67914,7 @@
         <v>614</v>
       </c>
       <c r="V9" s="170" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Z9" s="1" t="s">
         <v>46</v>
@@ -67932,7 +67943,7 @@
         <v>Amil - Hospital Ipiranga Arujá - Ambulatório </v>
       </c>
       <c r="M10" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N10" s="150" t="s">
         <v>616</v>
@@ -67941,13 +67952,13 @@
         <v>617</v>
       </c>
       <c r="V10" s="170" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Z10" s="1" t="s">
         <v>46</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AD10" s="83"/>
       <c r="AF10" s="83"/>
@@ -67966,7 +67977,7 @@
         <v>Amil - Hospital Ipiranga Mogi - Ambulatório </v>
       </c>
       <c r="M11" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N11" s="150" t="s">
         <v>619</v>
@@ -67975,7 +67986,7 @@
         <v>64</v>
       </c>
       <c r="V11" s="170" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="Z11" s="1" t="s">
         <v>71</v>
@@ -68001,7 +68012,7 @@
         <v>Amil - Hospital Metropolitano - Centro Médico </v>
       </c>
       <c r="M12" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N12" s="150" t="s">
         <v>621</v>
@@ -68010,13 +68021,13 @@
         <v>622</v>
       </c>
       <c r="V12" s="170" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AD12" s="83"/>
       <c r="AF12" s="83"/>
@@ -68036,7 +68047,7 @@
         <v>Amil - Hospital Paulistano - Ambulatório </v>
       </c>
       <c r="M13" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N13" s="150" t="s">
         <v>624</v>
@@ -68045,7 +68056,7 @@
         <v>625</v>
       </c>
       <c r="V13" s="170" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Z13" s="1" t="s">
         <v>58</v>
@@ -68071,7 +68082,7 @@
         <v>Amil - Ud Cubatão Sp - Hospital Da Luz </v>
       </c>
       <c r="M14" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N14" s="150" t="s">
         <v>97</v>
@@ -68080,10 +68091,10 @@
         <v>611</v>
       </c>
       <c r="V14" s="170" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AA14" s="1" t="s">
         <v>71</v>
@@ -68106,7 +68117,7 @@
         <v>Amil - Unidade Avançada Carlos Chagas </v>
       </c>
       <c r="M15" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N15" s="150" t="s">
         <v>628</v>
@@ -68118,10 +68129,10 @@
         <v>56</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AD15" s="83"/>
       <c r="AF15" s="83"/>
@@ -68141,7 +68152,7 @@
         <v>Amil - Unidade Avançada Luz Butantã </v>
       </c>
       <c r="M16" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N16" s="150" t="s">
         <v>631</v>
@@ -68150,10 +68161,10 @@
         <v>632</v>
       </c>
       <c r="V16" s="170" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AA16" s="1" t="s">
         <v>58</v>
@@ -68176,7 +68187,7 @@
         <v>Amil - Unidade Avançada Luz Joao Dias </v>
       </c>
       <c r="M17" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N17" s="150" t="s">
         <v>634</v>
@@ -68185,7 +68196,7 @@
         <v>635</v>
       </c>
       <c r="V17" s="170" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AD17" s="83"/>
       <c r="AF17" s="83"/>
@@ -68205,7 +68216,7 @@
         <v>Amil - Unidade Avançada Vitoria </v>
       </c>
       <c r="M18" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N18" s="150" t="s">
         <v>637</v>
@@ -68214,7 +68225,7 @@
         <v>638</v>
       </c>
       <c r="V18" s="170" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AD18" s="83"/>
       <c r="AF18" s="83"/>
@@ -68234,16 +68245,16 @@
         <v>Amil Espaço Saúde - Ana Rosa </v>
       </c>
       <c r="M19" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N19" s="150" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="R19" s="59" t="s">
         <v>640</v>
       </c>
       <c r="V19" s="170" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AD19" s="83"/>
       <c r="AF19" s="83"/>
@@ -68263,7 +68274,7 @@
         <v>Amil Espaço Saúde - Botafogo </v>
       </c>
       <c r="M20" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N20" s="150" t="s">
         <v>642</v>
@@ -68272,7 +68283,7 @@
         <v>643</v>
       </c>
       <c r="V20" s="170" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="Z20" s="1" t="str">
         <f>+Análise!$C$4</f>
@@ -68303,7 +68314,7 @@
         <v>Amil Espaço Saúde - Campo Grande </v>
       </c>
       <c r="M21" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N21" s="150" t="s">
         <v>646</v>
@@ -68312,7 +68323,7 @@
         <v>647</v>
       </c>
       <c r="V21" s="170" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AA21" s="1" t="str">
         <v>Inativo</v>
@@ -68338,7 +68349,7 @@
         <v>Amil Espaço Saúde - Caxias </v>
       </c>
       <c r="M22" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N22" s="150" t="s">
         <v>649</v>
@@ -68347,7 +68358,7 @@
         <v>650</v>
       </c>
       <c r="V22" s="170" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AA22" s="1" t="str">
         <v>Fora da Linha</v>
@@ -68373,7 +68384,7 @@
         <v>Amil Espaço Saúde - Guarulhos </v>
       </c>
       <c r="M23" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N23" s="150" t="s">
         <v>652</v>
@@ -68405,7 +68416,7 @@
         <v>Amil Espaço Saúde - Niterói </v>
       </c>
       <c r="M24" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N24" s="150" t="s">
         <v>655</v>
@@ -68414,7 +68425,7 @@
         <v>656</v>
       </c>
       <c r="V24" s="170" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AD24" s="83"/>
       <c r="AF24" s="83"/>
@@ -68434,13 +68445,13 @@
         <v>Amil Espaço Saúde - Nova Iguaçu </v>
       </c>
       <c r="M25" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N25" s="150" t="s">
         <v>658</v>
       </c>
       <c r="V25" s="170" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AD25" s="83"/>
       <c r="AF25" s="83"/>
@@ -68460,13 +68471,13 @@
         <v>Amil Espaço Saúde - Osasco </v>
       </c>
       <c r="M26" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N26" s="150" t="s">
         <v>660</v>
       </c>
       <c r="V26" s="171" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AD26" s="83"/>
       <c r="AF26" s="83"/>
@@ -68486,7 +68497,7 @@
         <v>Amil Espaço Saúde - Santana </v>
       </c>
       <c r="M27" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N27" s="150" t="s">
         <v>662</v>
@@ -68512,7 +68523,7 @@
         <v>Amil Espaço Saúde - Tijuca </v>
       </c>
       <c r="M28" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N28" s="150" t="s">
         <v>81</v>
@@ -68533,13 +68544,13 @@
         <v>Amil Telemedicina </v>
       </c>
       <c r="M29" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N29" s="150" t="s">
         <v>665</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="30" spans="6:38">
@@ -68554,7 +68565,7 @@
         <v>Centro Médico Jardim </v>
       </c>
       <c r="M30" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N30" s="150" t="s">
         <v>667</v>
@@ -68575,13 +68586,13 @@
         <v>Centro Médico Joao Azevedo - Sbc  II</v>
       </c>
       <c r="M31" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N31" s="150" t="s">
         <v>669</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="32" spans="6:38">
@@ -68596,7 +68607,7 @@
         <v>Centro Médico João Azevedo - Sbc I  </v>
       </c>
       <c r="M32" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N32" s="150" t="s">
         <v>671</v>
@@ -68614,7 +68625,7 @@
         <v>Centro Médico Luiz Ferreira - Sbc </v>
       </c>
       <c r="M33" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N33" s="150" t="s">
         <v>673</v>
@@ -68632,7 +68643,7 @@
         <v>Centro Médico - Samaritano Higienópolis </v>
       </c>
       <c r="M34" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N34" s="150" t="s">
         <v>675</v>
@@ -68650,7 +68661,7 @@
         <v>Centro Médico Hospital São Lucas </v>
       </c>
       <c r="M35" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N35" s="150" t="s">
         <v>677</v>
@@ -68668,7 +68679,7 @@
         <v>Hospital Alvorada Ambulatório Arapanés </v>
       </c>
       <c r="M36" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N36" s="150" t="s">
         <v>679</v>
@@ -68686,7 +68697,7 @@
         <v>Hospital Alvorada Moema </v>
       </c>
       <c r="M37" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N37" s="150" t="s">
         <v>681</v>
@@ -68704,7 +68715,7 @@
         <v>Hospital Américas - Ambulatório </v>
       </c>
       <c r="M38" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N38" s="150" t="s">
         <v>683</v>
@@ -68722,7 +68733,7 @@
         <v>Hospital Samaritano Paulista - Ambulatório </v>
       </c>
       <c r="M39" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N39" s="150" t="s">
         <v>685</v>
@@ -68770,7 +68781,7 @@
         <v>611</v>
       </c>
       <c r="I42" s="58" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="K42" s="60" t="str">
         <v>Amil Espaço Saúde - Guarulhos</v>
@@ -68839,7 +68850,7 @@
     <row r="46" spans="6:14">
       <c r="F46" s="68"/>
       <c r="H46" s="79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I46" s="149" t="s">
         <v>697</v>
@@ -68871,7 +68882,7 @@
     <row r="48" spans="6:14">
       <c r="F48" s="68"/>
       <c r="H48" s="230" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I48" s="231" t="s">
         <v>699</v>
@@ -68963,7 +68974,7 @@
     </row>
     <row r="56" spans="6:14">
       <c r="M56" s="199" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N56" s="200" t="s">
         <v>220</v>
@@ -68971,7 +68982,7 @@
     </row>
     <row r="57" spans="6:14">
       <c r="M57" s="199" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N57" s="200" t="s">
         <v>223</v>
@@ -68979,7 +68990,7 @@
     </row>
     <row r="58" spans="6:14">
       <c r="M58" s="199" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N58" s="200" t="s">
         <v>90</v>
@@ -68987,7 +68998,7 @@
     </row>
     <row r="59" spans="6:14">
       <c r="M59" s="199" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N59" s="201" t="s">
         <v>708</v>
@@ -68995,15 +69006,15 @@
     </row>
     <row r="60" spans="6:14">
       <c r="M60" s="199" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N60" s="202" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="61" spans="6:14">
       <c r="M61" s="199" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N61" s="202" t="s">
         <v>709</v>
@@ -69215,10 +69226,10 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -69233,7 +69244,7 @@
       <c r="O3" s="17"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="19" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -69241,18 +69252,18 @@
         <v>183</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3" t="s">
@@ -69263,7 +69274,7 @@
         <v>714</v>
       </c>
       <c r="AG3" s="17" t="s">
-        <v>264</v>
+        <v>601</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -69273,7 +69284,7 @@
         <v>715</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -69288,12 +69299,12 @@
       <c r="O4" s="17"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="19" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
@@ -69309,7 +69320,7 @@
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AE4" s="3"/>
       <c r="AF4" s="3" t="s">
@@ -69323,7 +69334,7 @@
       <c r="M5" s="1"/>
       <c r="O5" s="1"/>
       <c r="Q5" s="22" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AB5" s="3" t="s">
         <v>61</v>
@@ -69336,7 +69347,7 @@
       <c r="M6" s="1"/>
       <c r="O6" s="1"/>
       <c r="Q6" s="23" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AF6" t="s">
         <v>718</v>
@@ -69346,7 +69357,7 @@
       <c r="M7" s="1"/>
       <c r="O7" s="1"/>
       <c r="Q7" s="23" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AF7" t="s">
         <v>719</v>
@@ -69356,7 +69367,7 @@
       <c r="M8" s="1"/>
       <c r="O8" s="1"/>
       <c r="Q8" s="23" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AF8" t="s">
         <v>720</v>
@@ -69366,7 +69377,7 @@
       <c r="M9" s="1"/>
       <c r="O9" s="1"/>
       <c r="Q9" s="23" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AF9" t="s">
         <v>721</v>
@@ -69376,7 +69387,7 @@
       <c r="M10" s="1"/>
       <c r="O10" s="1"/>
       <c r="Q10" s="23" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AF10" t="s">
         <v>722</v>
@@ -69389,7 +69400,7 @@
       <c r="M11" s="1"/>
       <c r="O11" s="1"/>
       <c r="Q11" s="23" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AF11" t="s">
         <v>724</v>
@@ -69399,21 +69410,21 @@
       <c r="M12" s="1"/>
       <c r="O12" s="1"/>
       <c r="Q12" s="23" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="13" spans="1:33">
       <c r="M13" s="1"/>
       <c r="O13" s="1"/>
       <c r="Q13" s="23" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="14" spans="1:33">
       <c r="M14" s="1"/>
       <c r="O14" s="1"/>
       <c r="Q14" s="23" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15" spans="1:33">
@@ -69427,14 +69438,14 @@
       <c r="M16" s="1"/>
       <c r="O16" s="1"/>
       <c r="Q16" s="23" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="17" spans="13:33">
       <c r="M17" s="1"/>
       <c r="O17" s="1"/>
       <c r="Q17" s="23" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AF17" t="s">
         <v>725</v>
@@ -69444,20 +69455,20 @@
       <c r="M18" s="1"/>
       <c r="O18" s="1"/>
       <c r="Q18" s="23" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AF18" s="24" t="s">
         <v>711</v>
       </c>
       <c r="AG18" s="24" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="19" spans="13:33">
       <c r="M19" s="1"/>
       <c r="O19" s="1"/>
       <c r="Q19" s="23" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AF19" t="s">
         <v>726</v>
@@ -69470,7 +69481,7 @@
       <c r="M20" s="1"/>
       <c r="O20" s="1"/>
       <c r="Q20" s="23" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AF20" t="s">
         <v>727</v>
@@ -69483,7 +69494,7 @@
       <c r="M21" s="1"/>
       <c r="O21" s="1"/>
       <c r="Q21" s="23" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG21" t="s">
         <v>728</v>
@@ -69493,7 +69504,7 @@
       <c r="M22" s="1"/>
       <c r="O22" s="1"/>
       <c r="Q22" s="23" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="23" spans="13:33">
@@ -69507,21 +69518,21 @@
       <c r="M24" s="1"/>
       <c r="O24" s="1"/>
       <c r="Q24" s="23" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="13:33">
       <c r="M25" s="1"/>
       <c r="O25" s="1"/>
       <c r="Q25" s="23" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="26" spans="13:33">
       <c r="M26" s="1"/>
       <c r="O26" s="1"/>
       <c r="Q26" s="23" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="27" spans="13:33">
@@ -69568,27 +69579,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f89f1a61-222e-42b3-980e-c03b4142086e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="245f25f3-ef55-4cde-9cd4-e19c029b0701" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="f89f1a61-222e-42b3-980e-c03b4142086e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100BE7C980CA93E054E939C59CBF8DCCA7B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="17a152ab00c190a4dea0369caab8215c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f89f1a61-222e-42b3-980e-c03b4142086e" xmlns:ns3="245f25f3-ef55-4cde-9cd4-e19c029b0701" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bb54a9478fd58f65db69e3e81781d4c" ns2:_="" ns3:_="">
     <xsd:import namespace="f89f1a61-222e-42b3-980e-c03b4142086e"/>
@@ -69823,16 +69813,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f89f1a61-222e-42b3-980e-c03b4142086e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="245f25f3-ef55-4cde-9cd4-e19c029b0701" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="f89f1a61-222e-42b3-980e-c03b4142086e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70F7B7A9-923F-47C9-B035-F75FFDCA5F1C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDEE90B0-5810-4985-9892-603D6D77939D}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C7276F3-723F-45C7-96FF-74194C59BEA3}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70F7B7A9-923F-47C9-B035-F75FFDCA5F1C}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
